--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sudebinici/Downloads/metricv2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA794AED-518C-BD42-BD29-402FF612BE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B04880-4CF9-2041-8EB4-EA4FBFCB9B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61993,7 +61993,7 @@
         <v>591</v>
       </c>
       <c r="F401" s="16" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="G401" s="16" t="s">
         <v>77</v>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15618" uniqueCount="1730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15803" uniqueCount="1750">
   <si>
     <t>Kank</t>
   </si>
@@ -5202,6 +5202,66 @@
   </si>
   <si>
     <t>ds^{2} = 2 \frac{(dx^{2} + dy^{2})}{(\lambda x)^{2}} - 2\,du \left[ dv + 2v\,dx/x + \frac{4x}{3\lambda}\,dy + 2x^{4} \right]</t>
+  </si>
+  <si>
+    <t>Kerr-Newman Spacetime</t>
+  </si>
+  <si>
+    <t>kerr-newman spacetime.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> kerr-newman spacetime.ipynb</t>
+  </si>
+  <si>
+    <t>ds^{2} = -\left(1 - \frac{2Mr - Q^{2}}{\Sigma}\right)dt^{2} + \frac{\Sigma}{\Delta}\,dr^{2} + \Sigma\,d\theta^{2} + \frac{\sin^{2}\theta}{\Sigma} \left[(r^{2} + a^{2})^{2} - a^{2}\Delta \sin^{2}\theta\right] d\phi^{2} - \frac{2a(2Mr - Q^{2})\sin^{2}\theta}{\Sigma}\,dt\,d\phi.</t>
+  </si>
+  <si>
+    <t>The Wahlquist-Newman Spacetime</t>
+  </si>
+  <si>
+    <t>Wahlquist-Newman.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Wahlquist–Newman.ipynb</t>
+  </si>
+  <si>
+    <t>ds^{2} = -\frac{V_{1}}{v_{1} + v_{2}} (d\tau - v_{1}\,d\sigma)^{2} + \frac{U_{1}}{v_{1} + v_{2}} (d\tau + v_{2}\,d\sigma)^{2} + (v_{1} + v_{2}) \left( \frac{dy^{2}}{V_{1}} + \frac{dz^{2}}{U_{1}} \right),</t>
+  </si>
+  <si>
+    <t>Kerr-Newman Anti de Sitter</t>
+  </si>
+  <si>
+    <t>kerr-newman anti de sitter.pdf</t>
+  </si>
+  <si>
+    <t>kerr-newman anti de sitter.ipynb</t>
+  </si>
+  <si>
+    <t>ds^{2} = -\frac{\Delta_{r}}{\Xi^{2}\rho^{2}} \left(d\bar{t} - a\sin^{2}\theta\,d\bar{\phi}\right)^{2} + \frac{\rho^{2}}{\Delta_{r}}\,dr^{2} + \frac{\rho^{2}}{\Delta_{\theta}}\,d\theta^{2} + \frac{\Delta_{\theta}\sin^{2}\theta}{\Xi^{2}\rho^{2}} \left[a\,d\bar{t} - (r^{2} + a^{2})\,d\bar{\phi}\right]^{2},</t>
+  </si>
+  <si>
+    <t>The Rotating Charged C Metric</t>
+  </si>
+  <si>
+    <t>The_Rotating_Charged_C_Metric.pdf</t>
+  </si>
+  <si>
+    <t>The Rotating Charged C Metric.ipynb</t>
+  </si>
+  <si>
+    <t>ds^{2} = \frac{B^{2}}{A^{2}(x - y)^{2}} \left\{ \frac{\mathcal{G}(y)}{\mathcal{D}} \left[(1 + a^{2}A^{2}x^{2})K_{\tau}\,d\tau + aA(1 - x^{2})K_{\varphi}\,d\varphi\right]^{2} - \frac{\mathcal{D}}{\mathcal{G}(y)}\,dy^{2} + \frac{\mathcal{D}}{\mathcal{G}(x)}\,dx^{2} + \frac{\mathcal{G}(x)}{\mathcal{D}} \left[(1 + a^{2}A^{2}y^{2})K_{\varphi}\,d\varphi - aA(1 - y^{2})K_{\tau}\,d\tau\right]^{2} \right\},</t>
+  </si>
+  <si>
+    <t>The Wahlquist Metric</t>
+  </si>
+  <si>
+    <t>The_Wahlquist_Metric.pdf</t>
+  </si>
+  <si>
+    <t>Wahlquist.ipynb</t>
+  </si>
+  <si>
+    <t>ds^{2} = (v_{1} + v_{2}) \left( \frac{dz^{2}}{U} + \frac{dw^{2}}{V} \right) + \frac{U}{v_{1} + v_{2}} (d\tau + v_{2}\,d\sigma)^{2} - \frac{V}{v_{1} + v_{2}} (d\tau - v_{1}\,d\sigma)^{2},</t>
   </si>
 </sst>
 </file>
@@ -5348,7 +5408,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -5548,13 +5608,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -7681,7 +7747,7 @@
         <v>57</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="14" t="s">
@@ -7706,13 +7772,13 @@
         <v>50</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R14" s="14" t="s">
         <v>50</v>
       </c>
       <c r="S14" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T14" s="14" t="s">
         <v>50</v>
@@ -7721,10 +7787,10 @@
         <v>50</v>
       </c>
       <c r="V14" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="W14" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="X14" s="14" t="s">
         <v>50</v>
@@ -7754,22 +7820,22 @@
         <v>50</v>
       </c>
       <c r="AG14" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AH14" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AI14" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AJ14" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AK14" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AL14" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AM14" s="16" t="s">
         <v>44</v>
@@ -7778,7 +7844,7 @@
         <v>62</v>
       </c>
       <c r="AO14" s="14" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="AP14" s="17" t="s">
         <v>120</v>
@@ -67417,46 +67483,120 @@
     <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="65"/>
       <c r="B435" s="15"/>
-      <c r="C435" s="66"/>
+      <c r="C435" s="66" t="s">
+        <v>1730</v>
+      </c>
       <c r="D435" s="67"/>
       <c r="E435" s="67"/>
-      <c r="F435" s="66"/>
-      <c r="G435" s="66"/>
-      <c r="H435" s="68"/>
+      <c r="F435" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="G435" s="66" t="s">
+        <v>692</v>
+      </c>
+      <c r="H435" s="38" t="s">
+        <v>89</v>
+      </c>
       <c r="I435" s="68"/>
-      <c r="J435" s="68"/>
-      <c r="K435" s="68"/>
-      <c r="L435" s="66"/>
-      <c r="M435" s="66"/>
-      <c r="N435" s="66"/>
-      <c r="O435" s="66"/>
-      <c r="P435" s="66"/>
-      <c r="Q435" s="66"/>
-      <c r="R435" s="66"/>
-      <c r="S435" s="66"/>
-      <c r="T435" s="66"/>
-      <c r="U435" s="66"/>
-      <c r="V435" s="66"/>
-      <c r="W435" s="66"/>
-      <c r="X435" s="66"/>
-      <c r="Y435" s="66"/>
-      <c r="Z435" s="66"/>
-      <c r="AA435" s="66"/>
-      <c r="AB435" s="66"/>
-      <c r="AC435" s="66"/>
-      <c r="AD435" s="66"/>
-      <c r="AE435" s="66"/>
-      <c r="AF435" s="66"/>
-      <c r="AG435" s="66"/>
-      <c r="AH435" s="66"/>
-      <c r="AI435" s="66"/>
-      <c r="AJ435" s="66"/>
-      <c r="AK435" s="66"/>
-      <c r="AL435" s="66"/>
-      <c r="AM435" s="66"/>
-      <c r="AN435" s="66"/>
-      <c r="AO435" s="68"/>
-      <c r="AP435" s="69"/>
+      <c r="J435" s="38" t="s">
+        <v>1731</v>
+      </c>
+      <c r="K435" s="38" t="s">
+        <v>1732</v>
+      </c>
+      <c r="L435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="M435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="N435" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="O435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="P435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="R435" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="S435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="T435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="U435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="V435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="W435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="X435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA435" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB435" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE435" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF435" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG435" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH435" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI435" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL435" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM435" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN435" s="66" t="s">
+        <v>696</v>
+      </c>
+      <c r="AO435" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP435" s="69" t="s">
+        <v>1733</v>
+      </c>
       <c r="AQ435" s="12"/>
       <c r="AR435" s="12"/>
       <c r="AS435" s="12"/>
@@ -67480,46 +67620,120 @@
     <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="65"/>
       <c r="B436" s="15"/>
-      <c r="C436" s="66"/>
+      <c r="C436" s="66" t="s">
+        <v>1734</v>
+      </c>
       <c r="D436" s="67"/>
       <c r="E436" s="67"/>
-      <c r="F436" s="66"/>
-      <c r="G436" s="66"/>
-      <c r="H436" s="68"/>
+      <c r="F436" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="G436" s="66" t="s">
+        <v>692</v>
+      </c>
+      <c r="H436" s="38" t="s">
+        <v>89</v>
+      </c>
       <c r="I436" s="68"/>
-      <c r="J436" s="68"/>
-      <c r="K436" s="68"/>
-      <c r="L436" s="66"/>
-      <c r="M436" s="66"/>
-      <c r="N436" s="66"/>
-      <c r="O436" s="66"/>
-      <c r="P436" s="66"/>
-      <c r="Q436" s="66"/>
-      <c r="R436" s="66"/>
-      <c r="S436" s="66"/>
-      <c r="T436" s="66"/>
-      <c r="U436" s="66"/>
-      <c r="V436" s="66"/>
-      <c r="W436" s="66"/>
-      <c r="X436" s="66"/>
-      <c r="Y436" s="66"/>
-      <c r="Z436" s="66"/>
-      <c r="AA436" s="66"/>
-      <c r="AB436" s="66"/>
-      <c r="AC436" s="66"/>
-      <c r="AD436" s="66"/>
-      <c r="AE436" s="66"/>
-      <c r="AF436" s="66"/>
-      <c r="AG436" s="66"/>
-      <c r="AH436" s="66"/>
-      <c r="AI436" s="66"/>
-      <c r="AJ436" s="66"/>
-      <c r="AK436" s="66"/>
-      <c r="AL436" s="66"/>
-      <c r="AM436" s="66"/>
-      <c r="AN436" s="66"/>
-      <c r="AO436" s="68"/>
-      <c r="AP436" s="69"/>
+      <c r="J436" s="38" t="s">
+        <v>1735</v>
+      </c>
+      <c r="K436" s="38" t="s">
+        <v>1736</v>
+      </c>
+      <c r="L436" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="M436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="N436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="O436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="P436" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="R436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="S436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="T436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="U436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="V436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="W436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="X436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z436" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA436" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB436" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC436" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD436" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE436" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF436" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG436" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH436" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI436" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ436" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK436" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL436" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM436" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="AN436" s="66" t="s">
+        <v>696</v>
+      </c>
+      <c r="AO436" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP436" s="69" t="s">
+        <v>1737</v>
+      </c>
       <c r="AQ436" s="12"/>
       <c r="AR436" s="12"/>
       <c r="AS436" s="12"/>
@@ -67543,46 +67757,120 @@
     <row r="437" ht="15.75" customHeight="1">
       <c r="A437" s="65"/>
       <c r="B437" s="15"/>
-      <c r="C437" s="66"/>
+      <c r="C437" s="66" t="s">
+        <v>1738</v>
+      </c>
       <c r="D437" s="67"/>
       <c r="E437" s="67"/>
-      <c r="F437" s="66"/>
-      <c r="G437" s="66"/>
-      <c r="H437" s="68"/>
+      <c r="F437" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="G437" s="66" t="s">
+        <v>692</v>
+      </c>
+      <c r="H437" s="14" t="s">
+        <v>540</v>
+      </c>
       <c r="I437" s="68"/>
-      <c r="J437" s="68"/>
-      <c r="K437" s="68"/>
-      <c r="L437" s="66"/>
-      <c r="M437" s="66"/>
-      <c r="N437" s="66"/>
-      <c r="O437" s="66"/>
-      <c r="P437" s="66"/>
-      <c r="Q437" s="66"/>
-      <c r="R437" s="66"/>
-      <c r="S437" s="66"/>
-      <c r="T437" s="66"/>
-      <c r="U437" s="66"/>
-      <c r="V437" s="66"/>
-      <c r="W437" s="66"/>
-      <c r="X437" s="66"/>
-      <c r="Y437" s="66"/>
-      <c r="Z437" s="66"/>
-      <c r="AA437" s="66"/>
-      <c r="AB437" s="66"/>
-      <c r="AC437" s="66"/>
-      <c r="AD437" s="66"/>
-      <c r="AE437" s="66"/>
-      <c r="AF437" s="66"/>
-      <c r="AG437" s="66"/>
-      <c r="AH437" s="66"/>
-      <c r="AI437" s="66"/>
-      <c r="AJ437" s="66"/>
-      <c r="AK437" s="66"/>
-      <c r="AL437" s="66"/>
-      <c r="AM437" s="66"/>
-      <c r="AN437" s="66"/>
-      <c r="AO437" s="68"/>
-      <c r="AP437" s="69"/>
+      <c r="J437" s="38" t="s">
+        <v>1739</v>
+      </c>
+      <c r="K437" s="38" t="s">
+        <v>1740</v>
+      </c>
+      <c r="L437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="M437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="N437" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="O437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="P437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="R437" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="S437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="T437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="U437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="V437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="W437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="X437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z437" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA437" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB437" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE437" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF437" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG437" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH437" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI437" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL437" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM437" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN437" s="66" t="s">
+        <v>696</v>
+      </c>
+      <c r="AO437" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="AP437" s="69" t="s">
+        <v>1741</v>
+      </c>
       <c r="AQ437" s="12"/>
       <c r="AR437" s="12"/>
       <c r="AS437" s="12"/>
@@ -67606,46 +67894,120 @@
     <row r="438" ht="15.75" customHeight="1">
       <c r="A438" s="65"/>
       <c r="B438" s="15"/>
-      <c r="C438" s="66"/>
+      <c r="C438" s="66" t="s">
+        <v>1742</v>
+      </c>
       <c r="D438" s="67"/>
       <c r="E438" s="67"/>
-      <c r="F438" s="66"/>
-      <c r="G438" s="66"/>
-      <c r="H438" s="68"/>
+      <c r="F438" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="G438" s="66" t="s">
+        <v>692</v>
+      </c>
+      <c r="H438" s="38" t="s">
+        <v>89</v>
+      </c>
       <c r="I438" s="68"/>
-      <c r="J438" s="68"/>
-      <c r="K438" s="68"/>
-      <c r="L438" s="66"/>
-      <c r="M438" s="66"/>
-      <c r="N438" s="66"/>
-      <c r="O438" s="66"/>
-      <c r="P438" s="66"/>
-      <c r="Q438" s="66"/>
-      <c r="R438" s="66"/>
-      <c r="S438" s="66"/>
-      <c r="T438" s="66"/>
-      <c r="U438" s="66"/>
-      <c r="V438" s="66"/>
-      <c r="W438" s="66"/>
-      <c r="X438" s="66"/>
-      <c r="Y438" s="66"/>
-      <c r="Z438" s="66"/>
-      <c r="AA438" s="66"/>
-      <c r="AB438" s="66"/>
-      <c r="AC438" s="66"/>
-      <c r="AD438" s="66"/>
-      <c r="AE438" s="66"/>
-      <c r="AF438" s="66"/>
-      <c r="AG438" s="66"/>
-      <c r="AH438" s="66"/>
-      <c r="AI438" s="66"/>
-      <c r="AJ438" s="66"/>
-      <c r="AK438" s="66"/>
-      <c r="AL438" s="66"/>
-      <c r="AM438" s="66"/>
-      <c r="AN438" s="66"/>
-      <c r="AO438" s="68"/>
-      <c r="AP438" s="69"/>
+      <c r="J438" s="38" t="s">
+        <v>1743</v>
+      </c>
+      <c r="K438" s="38" t="s">
+        <v>1744</v>
+      </c>
+      <c r="L438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="M438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="N438" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="O438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="P438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="R438" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="S438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="T438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="U438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="V438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="W438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="X438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z438" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA438" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB438" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE438" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF438" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG438" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH438" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI438" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ438" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL438" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM438" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN438" s="66" t="s">
+        <v>696</v>
+      </c>
+      <c r="AO438" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP438" s="69" t="s">
+        <v>1745</v>
+      </c>
       <c r="AQ438" s="12"/>
       <c r="AR438" s="12"/>
       <c r="AS438" s="12"/>
@@ -67669,46 +68031,120 @@
     <row r="439" ht="15.75" customHeight="1">
       <c r="A439" s="65"/>
       <c r="B439" s="15"/>
-      <c r="C439" s="66"/>
+      <c r="C439" s="66" t="s">
+        <v>1746</v>
+      </c>
       <c r="D439" s="67"/>
       <c r="E439" s="67"/>
-      <c r="F439" s="66"/>
-      <c r="G439" s="66"/>
-      <c r="H439" s="68"/>
+      <c r="F439" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="G439" s="66" t="s">
+        <v>692</v>
+      </c>
+      <c r="H439" s="38" t="s">
+        <v>146</v>
+      </c>
       <c r="I439" s="68"/>
-      <c r="J439" s="68"/>
-      <c r="K439" s="68"/>
-      <c r="L439" s="66"/>
-      <c r="M439" s="66"/>
-      <c r="N439" s="66"/>
-      <c r="O439" s="66"/>
-      <c r="P439" s="66"/>
-      <c r="Q439" s="66"/>
-      <c r="R439" s="66"/>
-      <c r="S439" s="66"/>
-      <c r="T439" s="66"/>
-      <c r="U439" s="66"/>
-      <c r="V439" s="66"/>
-      <c r="W439" s="66"/>
-      <c r="X439" s="66"/>
-      <c r="Y439" s="66"/>
-      <c r="Z439" s="66"/>
-      <c r="AA439" s="66"/>
-      <c r="AB439" s="66"/>
-      <c r="AC439" s="66"/>
-      <c r="AD439" s="66"/>
-      <c r="AE439" s="66"/>
-      <c r="AF439" s="66"/>
-      <c r="AG439" s="66"/>
-      <c r="AH439" s="66"/>
-      <c r="AI439" s="66"/>
-      <c r="AJ439" s="66"/>
-      <c r="AK439" s="66"/>
-      <c r="AL439" s="66"/>
-      <c r="AM439" s="66"/>
-      <c r="AN439" s="66"/>
-      <c r="AO439" s="68"/>
-      <c r="AP439" s="69"/>
+      <c r="J439" s="38" t="s">
+        <v>1747</v>
+      </c>
+      <c r="K439" s="38" t="s">
+        <v>1748</v>
+      </c>
+      <c r="L439" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="M439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="N439" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="O439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="P439" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="R439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="S439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="T439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="U439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="V439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="W439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="X439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z439" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA439" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB439" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC439" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD439" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE439" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF439" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG439" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH439" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI439" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ439" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK439" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL439" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM439" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="AN439" s="66" t="s">
+        <v>696</v>
+      </c>
+      <c r="AO439" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="AP439" s="69" t="s">
+        <v>1749</v>
+      </c>
       <c r="AQ439" s="12"/>
       <c r="AR439" s="12"/>
       <c r="AS439" s="12"/>
@@ -67732,46 +68168,46 @@
     <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="65"/>
       <c r="B440" s="15"/>
-      <c r="C440" s="66"/>
+      <c r="C440" s="70"/>
       <c r="D440" s="67"/>
       <c r="E440" s="67"/>
-      <c r="F440" s="66"/>
-      <c r="G440" s="66"/>
+      <c r="F440" s="70"/>
+      <c r="G440" s="70"/>
       <c r="H440" s="68"/>
       <c r="I440" s="68"/>
       <c r="J440" s="68"/>
       <c r="K440" s="68"/>
-      <c r="L440" s="66"/>
-      <c r="M440" s="66"/>
-      <c r="N440" s="66"/>
-      <c r="O440" s="66"/>
-      <c r="P440" s="66"/>
-      <c r="Q440" s="66"/>
-      <c r="R440" s="66"/>
-      <c r="S440" s="66"/>
-      <c r="T440" s="66"/>
-      <c r="U440" s="66"/>
-      <c r="V440" s="66"/>
-      <c r="W440" s="66"/>
-      <c r="X440" s="66"/>
-      <c r="Y440" s="66"/>
-      <c r="Z440" s="66"/>
-      <c r="AA440" s="66"/>
-      <c r="AB440" s="66"/>
-      <c r="AC440" s="66"/>
-      <c r="AD440" s="66"/>
-      <c r="AE440" s="66"/>
-      <c r="AF440" s="66"/>
-      <c r="AG440" s="66"/>
-      <c r="AH440" s="66"/>
-      <c r="AI440" s="66"/>
-      <c r="AJ440" s="66"/>
-      <c r="AK440" s="66"/>
-      <c r="AL440" s="66"/>
-      <c r="AM440" s="66"/>
-      <c r="AN440" s="66"/>
+      <c r="L440" s="70"/>
+      <c r="M440" s="70"/>
+      <c r="N440" s="70"/>
+      <c r="O440" s="70"/>
+      <c r="P440" s="70"/>
+      <c r="Q440" s="70"/>
+      <c r="R440" s="70"/>
+      <c r="S440" s="70"/>
+      <c r="T440" s="70"/>
+      <c r="U440" s="70"/>
+      <c r="V440" s="70"/>
+      <c r="W440" s="70"/>
+      <c r="X440" s="70"/>
+      <c r="Y440" s="70"/>
+      <c r="Z440" s="70"/>
+      <c r="AA440" s="70"/>
+      <c r="AB440" s="70"/>
+      <c r="AC440" s="70"/>
+      <c r="AD440" s="70"/>
+      <c r="AE440" s="70"/>
+      <c r="AF440" s="70"/>
+      <c r="AG440" s="70"/>
+      <c r="AH440" s="70"/>
+      <c r="AI440" s="70"/>
+      <c r="AJ440" s="70"/>
+      <c r="AK440" s="70"/>
+      <c r="AL440" s="70"/>
+      <c r="AM440" s="70"/>
+      <c r="AN440" s="70"/>
       <c r="AO440" s="68"/>
-      <c r="AP440" s="69"/>
+      <c r="AP440" s="71"/>
       <c r="AQ440" s="12"/>
       <c r="AR440" s="12"/>
       <c r="AS440" s="12"/>
@@ -67795,46 +68231,46 @@
     <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="65"/>
       <c r="B441" s="15"/>
-      <c r="C441" s="66"/>
+      <c r="C441" s="70"/>
       <c r="D441" s="67"/>
       <c r="E441" s="67"/>
-      <c r="F441" s="66"/>
-      <c r="G441" s="66"/>
+      <c r="F441" s="70"/>
+      <c r="G441" s="70"/>
       <c r="H441" s="68"/>
       <c r="I441" s="68"/>
       <c r="J441" s="68"/>
       <c r="K441" s="68"/>
-      <c r="L441" s="66"/>
-      <c r="M441" s="66"/>
-      <c r="N441" s="66"/>
-      <c r="O441" s="66"/>
-      <c r="P441" s="66"/>
-      <c r="Q441" s="66"/>
-      <c r="R441" s="66"/>
-      <c r="S441" s="66"/>
-      <c r="T441" s="66"/>
-      <c r="U441" s="66"/>
-      <c r="V441" s="66"/>
-      <c r="W441" s="66"/>
-      <c r="X441" s="66"/>
-      <c r="Y441" s="66"/>
-      <c r="Z441" s="66"/>
-      <c r="AA441" s="66"/>
-      <c r="AB441" s="66"/>
-      <c r="AC441" s="66"/>
-      <c r="AD441" s="66"/>
-      <c r="AE441" s="66"/>
-      <c r="AF441" s="66"/>
-      <c r="AG441" s="66"/>
-      <c r="AH441" s="66"/>
-      <c r="AI441" s="66"/>
-      <c r="AJ441" s="66"/>
-      <c r="AK441" s="66"/>
-      <c r="AL441" s="66"/>
-      <c r="AM441" s="66"/>
-      <c r="AN441" s="66"/>
+      <c r="L441" s="70"/>
+      <c r="M441" s="70"/>
+      <c r="N441" s="70"/>
+      <c r="O441" s="70"/>
+      <c r="P441" s="70"/>
+      <c r="Q441" s="70"/>
+      <c r="R441" s="70"/>
+      <c r="S441" s="70"/>
+      <c r="T441" s="70"/>
+      <c r="U441" s="70"/>
+      <c r="V441" s="70"/>
+      <c r="W441" s="70"/>
+      <c r="X441" s="70"/>
+      <c r="Y441" s="70"/>
+      <c r="Z441" s="70"/>
+      <c r="AA441" s="70"/>
+      <c r="AB441" s="70"/>
+      <c r="AC441" s="70"/>
+      <c r="AD441" s="70"/>
+      <c r="AE441" s="70"/>
+      <c r="AF441" s="70"/>
+      <c r="AG441" s="70"/>
+      <c r="AH441" s="70"/>
+      <c r="AI441" s="70"/>
+      <c r="AJ441" s="70"/>
+      <c r="AK441" s="70"/>
+      <c r="AL441" s="70"/>
+      <c r="AM441" s="70"/>
+      <c r="AN441" s="70"/>
       <c r="AO441" s="68"/>
-      <c r="AP441" s="69"/>
+      <c r="AP441" s="71"/>
       <c r="AQ441" s="12"/>
       <c r="AR441" s="12"/>
       <c r="AS441" s="12"/>
@@ -67858,46 +68294,46 @@
     <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="65"/>
       <c r="B442" s="15"/>
-      <c r="C442" s="66"/>
+      <c r="C442" s="70"/>
       <c r="D442" s="67"/>
       <c r="E442" s="67"/>
-      <c r="F442" s="66"/>
-      <c r="G442" s="66"/>
+      <c r="F442" s="70"/>
+      <c r="G442" s="70"/>
       <c r="H442" s="68"/>
       <c r="I442" s="68"/>
       <c r="J442" s="68"/>
       <c r="K442" s="68"/>
-      <c r="L442" s="66"/>
-      <c r="M442" s="66"/>
-      <c r="N442" s="66"/>
-      <c r="O442" s="66"/>
-      <c r="P442" s="66"/>
-      <c r="Q442" s="66"/>
-      <c r="R442" s="66"/>
-      <c r="S442" s="66"/>
-      <c r="T442" s="66"/>
-      <c r="U442" s="66"/>
-      <c r="V442" s="66"/>
-      <c r="W442" s="66"/>
-      <c r="X442" s="66"/>
-      <c r="Y442" s="66"/>
-      <c r="Z442" s="66"/>
-      <c r="AA442" s="66"/>
-      <c r="AB442" s="66"/>
-      <c r="AC442" s="66"/>
-      <c r="AD442" s="66"/>
-      <c r="AE442" s="66"/>
-      <c r="AF442" s="66"/>
-      <c r="AG442" s="66"/>
-      <c r="AH442" s="66"/>
-      <c r="AI442" s="66"/>
-      <c r="AJ442" s="66"/>
-      <c r="AK442" s="66"/>
-      <c r="AL442" s="66"/>
-      <c r="AM442" s="66"/>
-      <c r="AN442" s="66"/>
+      <c r="L442" s="70"/>
+      <c r="M442" s="70"/>
+      <c r="N442" s="70"/>
+      <c r="O442" s="70"/>
+      <c r="P442" s="70"/>
+      <c r="Q442" s="70"/>
+      <c r="R442" s="70"/>
+      <c r="S442" s="70"/>
+      <c r="T442" s="70"/>
+      <c r="U442" s="70"/>
+      <c r="V442" s="70"/>
+      <c r="W442" s="70"/>
+      <c r="X442" s="70"/>
+      <c r="Y442" s="70"/>
+      <c r="Z442" s="70"/>
+      <c r="AA442" s="70"/>
+      <c r="AB442" s="70"/>
+      <c r="AC442" s="70"/>
+      <c r="AD442" s="70"/>
+      <c r="AE442" s="70"/>
+      <c r="AF442" s="70"/>
+      <c r="AG442" s="70"/>
+      <c r="AH442" s="70"/>
+      <c r="AI442" s="70"/>
+      <c r="AJ442" s="70"/>
+      <c r="AK442" s="70"/>
+      <c r="AL442" s="70"/>
+      <c r="AM442" s="70"/>
+      <c r="AN442" s="70"/>
       <c r="AO442" s="68"/>
-      <c r="AP442" s="69"/>
+      <c r="AP442" s="71"/>
       <c r="AQ442" s="12"/>
       <c r="AR442" s="12"/>
       <c r="AS442" s="12"/>
@@ -67921,46 +68357,46 @@
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="65"/>
       <c r="B443" s="15"/>
-      <c r="C443" s="66"/>
+      <c r="C443" s="70"/>
       <c r="D443" s="67"/>
       <c r="E443" s="67"/>
-      <c r="F443" s="66"/>
-      <c r="G443" s="66"/>
+      <c r="F443" s="70"/>
+      <c r="G443" s="70"/>
       <c r="H443" s="68"/>
       <c r="I443" s="68"/>
       <c r="J443" s="68"/>
       <c r="K443" s="68"/>
-      <c r="L443" s="66"/>
-      <c r="M443" s="66"/>
-      <c r="N443" s="66"/>
-      <c r="O443" s="66"/>
-      <c r="P443" s="66"/>
-      <c r="Q443" s="66"/>
-      <c r="R443" s="66"/>
-      <c r="S443" s="66"/>
-      <c r="T443" s="66"/>
-      <c r="U443" s="66"/>
-      <c r="V443" s="66"/>
-      <c r="W443" s="66"/>
-      <c r="X443" s="66"/>
-      <c r="Y443" s="66"/>
-      <c r="Z443" s="66"/>
-      <c r="AA443" s="66"/>
-      <c r="AB443" s="66"/>
-      <c r="AC443" s="66"/>
-      <c r="AD443" s="66"/>
-      <c r="AE443" s="66"/>
-      <c r="AF443" s="66"/>
-      <c r="AG443" s="66"/>
-      <c r="AH443" s="66"/>
-      <c r="AI443" s="66"/>
-      <c r="AJ443" s="66"/>
-      <c r="AK443" s="66"/>
-      <c r="AL443" s="66"/>
-      <c r="AM443" s="66"/>
-      <c r="AN443" s="66"/>
+      <c r="L443" s="70"/>
+      <c r="M443" s="70"/>
+      <c r="N443" s="70"/>
+      <c r="O443" s="70"/>
+      <c r="P443" s="70"/>
+      <c r="Q443" s="70"/>
+      <c r="R443" s="70"/>
+      <c r="S443" s="70"/>
+      <c r="T443" s="70"/>
+      <c r="U443" s="70"/>
+      <c r="V443" s="70"/>
+      <c r="W443" s="70"/>
+      <c r="X443" s="70"/>
+      <c r="Y443" s="70"/>
+      <c r="Z443" s="70"/>
+      <c r="AA443" s="70"/>
+      <c r="AB443" s="70"/>
+      <c r="AC443" s="70"/>
+      <c r="AD443" s="70"/>
+      <c r="AE443" s="70"/>
+      <c r="AF443" s="70"/>
+      <c r="AG443" s="70"/>
+      <c r="AH443" s="70"/>
+      <c r="AI443" s="70"/>
+      <c r="AJ443" s="70"/>
+      <c r="AK443" s="70"/>
+      <c r="AL443" s="70"/>
+      <c r="AM443" s="70"/>
+      <c r="AN443" s="70"/>
       <c r="AO443" s="68"/>
-      <c r="AP443" s="69"/>
+      <c r="AP443" s="71"/>
       <c r="AQ443" s="12"/>
       <c r="AR443" s="12"/>
       <c r="AS443" s="12"/>
@@ -67984,46 +68420,46 @@
     <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="65"/>
       <c r="B444" s="15"/>
-      <c r="C444" s="66"/>
+      <c r="C444" s="70"/>
       <c r="D444" s="67"/>
       <c r="E444" s="67"/>
-      <c r="F444" s="66"/>
-      <c r="G444" s="66"/>
+      <c r="F444" s="70"/>
+      <c r="G444" s="70"/>
       <c r="H444" s="68"/>
       <c r="I444" s="68"/>
       <c r="J444" s="68"/>
       <c r="K444" s="68"/>
-      <c r="L444" s="66"/>
-      <c r="M444" s="66"/>
-      <c r="N444" s="66"/>
-      <c r="O444" s="66"/>
-      <c r="P444" s="66"/>
-      <c r="Q444" s="66"/>
-      <c r="R444" s="66"/>
-      <c r="S444" s="66"/>
-      <c r="T444" s="66"/>
-      <c r="U444" s="66"/>
-      <c r="V444" s="66"/>
-      <c r="W444" s="66"/>
-      <c r="X444" s="66"/>
-      <c r="Y444" s="66"/>
-      <c r="Z444" s="66"/>
-      <c r="AA444" s="66"/>
-      <c r="AB444" s="66"/>
-      <c r="AC444" s="66"/>
-      <c r="AD444" s="66"/>
-      <c r="AE444" s="66"/>
-      <c r="AF444" s="66"/>
-      <c r="AG444" s="66"/>
-      <c r="AH444" s="66"/>
-      <c r="AI444" s="66"/>
-      <c r="AJ444" s="66"/>
-      <c r="AK444" s="66"/>
-      <c r="AL444" s="66"/>
-      <c r="AM444" s="66"/>
-      <c r="AN444" s="66"/>
+      <c r="L444" s="70"/>
+      <c r="M444" s="70"/>
+      <c r="N444" s="70"/>
+      <c r="O444" s="70"/>
+      <c r="P444" s="70"/>
+      <c r="Q444" s="70"/>
+      <c r="R444" s="70"/>
+      <c r="S444" s="70"/>
+      <c r="T444" s="70"/>
+      <c r="U444" s="70"/>
+      <c r="V444" s="70"/>
+      <c r="W444" s="70"/>
+      <c r="X444" s="70"/>
+      <c r="Y444" s="70"/>
+      <c r="Z444" s="70"/>
+      <c r="AA444" s="70"/>
+      <c r="AB444" s="70"/>
+      <c r="AC444" s="70"/>
+      <c r="AD444" s="70"/>
+      <c r="AE444" s="70"/>
+      <c r="AF444" s="70"/>
+      <c r="AG444" s="70"/>
+      <c r="AH444" s="70"/>
+      <c r="AI444" s="70"/>
+      <c r="AJ444" s="70"/>
+      <c r="AK444" s="70"/>
+      <c r="AL444" s="70"/>
+      <c r="AM444" s="70"/>
+      <c r="AN444" s="70"/>
       <c r="AO444" s="68"/>
-      <c r="AP444" s="69"/>
+      <c r="AP444" s="71"/>
       <c r="AQ444" s="12"/>
       <c r="AR444" s="12"/>
       <c r="AS444" s="12"/>
@@ -68047,46 +68483,46 @@
     <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="65"/>
       <c r="B445" s="15"/>
-      <c r="C445" s="66"/>
+      <c r="C445" s="70"/>
       <c r="D445" s="67"/>
       <c r="E445" s="67"/>
-      <c r="F445" s="66"/>
-      <c r="G445" s="66"/>
+      <c r="F445" s="70"/>
+      <c r="G445" s="70"/>
       <c r="H445" s="68"/>
       <c r="I445" s="68"/>
       <c r="J445" s="68"/>
       <c r="K445" s="68"/>
-      <c r="L445" s="66"/>
-      <c r="M445" s="66"/>
-      <c r="N445" s="66"/>
-      <c r="O445" s="66"/>
-      <c r="P445" s="66"/>
-      <c r="Q445" s="66"/>
-      <c r="R445" s="66"/>
-      <c r="S445" s="66"/>
-      <c r="T445" s="66"/>
-      <c r="U445" s="66"/>
-      <c r="V445" s="66"/>
-      <c r="W445" s="66"/>
-      <c r="X445" s="66"/>
-      <c r="Y445" s="66"/>
-      <c r="Z445" s="66"/>
-      <c r="AA445" s="66"/>
-      <c r="AB445" s="66"/>
-      <c r="AC445" s="66"/>
-      <c r="AD445" s="66"/>
-      <c r="AE445" s="66"/>
-      <c r="AF445" s="66"/>
-      <c r="AG445" s="66"/>
-      <c r="AH445" s="66"/>
-      <c r="AI445" s="66"/>
-      <c r="AJ445" s="66"/>
-      <c r="AK445" s="66"/>
-      <c r="AL445" s="66"/>
-      <c r="AM445" s="66"/>
-      <c r="AN445" s="66"/>
+      <c r="L445" s="70"/>
+      <c r="M445" s="70"/>
+      <c r="N445" s="70"/>
+      <c r="O445" s="70"/>
+      <c r="P445" s="70"/>
+      <c r="Q445" s="70"/>
+      <c r="R445" s="70"/>
+      <c r="S445" s="70"/>
+      <c r="T445" s="70"/>
+      <c r="U445" s="70"/>
+      <c r="V445" s="70"/>
+      <c r="W445" s="70"/>
+      <c r="X445" s="70"/>
+      <c r="Y445" s="70"/>
+      <c r="Z445" s="70"/>
+      <c r="AA445" s="70"/>
+      <c r="AB445" s="70"/>
+      <c r="AC445" s="70"/>
+      <c r="AD445" s="70"/>
+      <c r="AE445" s="70"/>
+      <c r="AF445" s="70"/>
+      <c r="AG445" s="70"/>
+      <c r="AH445" s="70"/>
+      <c r="AI445" s="70"/>
+      <c r="AJ445" s="70"/>
+      <c r="AK445" s="70"/>
+      <c r="AL445" s="70"/>
+      <c r="AM445" s="70"/>
+      <c r="AN445" s="70"/>
       <c r="AO445" s="68"/>
-      <c r="AP445" s="69"/>
+      <c r="AP445" s="71"/>
       <c r="AQ445" s="12"/>
       <c r="AR445" s="12"/>
       <c r="AS445" s="12"/>
@@ -68149,7 +68585,7 @@
       <c r="AM446" s="12"/>
       <c r="AN446" s="12"/>
       <c r="AO446" s="39"/>
-      <c r="AP446" s="69"/>
+      <c r="AP446" s="71"/>
       <c r="AQ446" s="12"/>
       <c r="AR446" s="12"/>
       <c r="AS446" s="12"/>
@@ -68212,7 +68648,7 @@
       <c r="AM447" s="12"/>
       <c r="AN447" s="12"/>
       <c r="AO447" s="39"/>
-      <c r="AP447" s="69"/>
+      <c r="AP447" s="71"/>
       <c r="AQ447" s="12"/>
       <c r="AR447" s="12"/>
       <c r="AS447" s="12"/>
@@ -68275,7 +68711,7 @@
       <c r="AM448" s="12"/>
       <c r="AN448" s="12"/>
       <c r="AO448" s="39"/>
-      <c r="AP448" s="69"/>
+      <c r="AP448" s="71"/>
       <c r="AQ448" s="12"/>
       <c r="AR448" s="12"/>
       <c r="AS448" s="12"/>
@@ -68338,7 +68774,7 @@
       <c r="AM449" s="12"/>
       <c r="AN449" s="12"/>
       <c r="AO449" s="39"/>
-      <c r="AP449" s="69"/>
+      <c r="AP449" s="71"/>
       <c r="AQ449" s="12"/>
       <c r="AR449" s="12"/>
       <c r="AS449" s="12"/>
@@ -68401,7 +68837,7 @@
       <c r="AM450" s="12"/>
       <c r="AN450" s="12"/>
       <c r="AO450" s="39"/>
-      <c r="AP450" s="69"/>
+      <c r="AP450" s="71"/>
       <c r="AQ450" s="12"/>
       <c r="AR450" s="12"/>
       <c r="AS450" s="12"/>
@@ -68464,7 +68900,7 @@
       <c r="AM451" s="12"/>
       <c r="AN451" s="12"/>
       <c r="AO451" s="39"/>
-      <c r="AP451" s="69"/>
+      <c r="AP451" s="71"/>
       <c r="AQ451" s="12"/>
       <c r="AR451" s="12"/>
       <c r="AS451" s="12"/>
@@ -68527,7 +68963,7 @@
       <c r="AM452" s="12"/>
       <c r="AN452" s="12"/>
       <c r="AO452" s="39"/>
-      <c r="AP452" s="69"/>
+      <c r="AP452" s="71"/>
       <c r="AQ452" s="12"/>
       <c r="AR452" s="12"/>
       <c r="AS452" s="12"/>
@@ -68590,7 +69026,7 @@
       <c r="AM453" s="12"/>
       <c r="AN453" s="12"/>
       <c r="AO453" s="39"/>
-      <c r="AP453" s="69"/>
+      <c r="AP453" s="71"/>
       <c r="AQ453" s="12"/>
       <c r="AR453" s="12"/>
       <c r="AS453" s="12"/>
@@ -68653,7 +69089,7 @@
       <c r="AM454" s="12"/>
       <c r="AN454" s="12"/>
       <c r="AO454" s="39"/>
-      <c r="AP454" s="69"/>
+      <c r="AP454" s="71"/>
       <c r="AQ454" s="12"/>
       <c r="AR454" s="12"/>
       <c r="AS454" s="12"/>
@@ -68716,7 +69152,7 @@
       <c r="AM455" s="12"/>
       <c r="AN455" s="12"/>
       <c r="AO455" s="39"/>
-      <c r="AP455" s="69"/>
+      <c r="AP455" s="71"/>
       <c r="AQ455" s="12"/>
       <c r="AR455" s="12"/>
       <c r="AS455" s="12"/>
@@ -68779,7 +69215,7 @@
       <c r="AM456" s="12"/>
       <c r="AN456" s="12"/>
       <c r="AO456" s="39"/>
-      <c r="AP456" s="69"/>
+      <c r="AP456" s="71"/>
       <c r="AQ456" s="12"/>
       <c r="AR456" s="12"/>
       <c r="AS456" s="12"/>
@@ -68842,7 +69278,7 @@
       <c r="AM457" s="12"/>
       <c r="AN457" s="12"/>
       <c r="AO457" s="39"/>
-      <c r="AP457" s="69"/>
+      <c r="AP457" s="71"/>
       <c r="AQ457" s="12"/>
       <c r="AR457" s="12"/>
       <c r="AS457" s="12"/>
@@ -68905,7 +69341,7 @@
       <c r="AM458" s="12"/>
       <c r="AN458" s="12"/>
       <c r="AO458" s="39"/>
-      <c r="AP458" s="69"/>
+      <c r="AP458" s="71"/>
       <c r="AQ458" s="12"/>
       <c r="AR458" s="12"/>
       <c r="AS458" s="12"/>
@@ -68968,7 +69404,7 @@
       <c r="AM459" s="12"/>
       <c r="AN459" s="12"/>
       <c r="AO459" s="39"/>
-      <c r="AP459" s="69"/>
+      <c r="AP459" s="71"/>
       <c r="AQ459" s="12"/>
       <c r="AR459" s="12"/>
       <c r="AS459" s="12"/>
@@ -69031,7 +69467,7 @@
       <c r="AM460" s="12"/>
       <c r="AN460" s="12"/>
       <c r="AO460" s="39"/>
-      <c r="AP460" s="69"/>
+      <c r="AP460" s="71"/>
       <c r="AQ460" s="12"/>
       <c r="AR460" s="12"/>
       <c r="AS460" s="12"/>
@@ -69094,7 +69530,7 @@
       <c r="AM461" s="12"/>
       <c r="AN461" s="12"/>
       <c r="AO461" s="39"/>
-      <c r="AP461" s="69"/>
+      <c r="AP461" s="71"/>
       <c r="AQ461" s="12"/>
       <c r="AR461" s="12"/>
       <c r="AS461" s="12"/>
@@ -69157,7 +69593,7 @@
       <c r="AM462" s="12"/>
       <c r="AN462" s="12"/>
       <c r="AO462" s="39"/>
-      <c r="AP462" s="69"/>
+      <c r="AP462" s="71"/>
       <c r="AQ462" s="12"/>
       <c r="AR462" s="12"/>
       <c r="AS462" s="12"/>
@@ -69220,7 +69656,7 @@
       <c r="AM463" s="12"/>
       <c r="AN463" s="12"/>
       <c r="AO463" s="39"/>
-      <c r="AP463" s="69"/>
+      <c r="AP463" s="71"/>
       <c r="AQ463" s="12"/>
       <c r="AR463" s="12"/>
       <c r="AS463" s="12"/>
@@ -69283,7 +69719,7 @@
       <c r="AM464" s="12"/>
       <c r="AN464" s="12"/>
       <c r="AO464" s="39"/>
-      <c r="AP464" s="69"/>
+      <c r="AP464" s="71"/>
       <c r="AQ464" s="12"/>
       <c r="AR464" s="12"/>
       <c r="AS464" s="12"/>
@@ -69346,7 +69782,7 @@
       <c r="AM465" s="12"/>
       <c r="AN465" s="12"/>
       <c r="AO465" s="39"/>
-      <c r="AP465" s="69"/>
+      <c r="AP465" s="71"/>
       <c r="AQ465" s="12"/>
       <c r="AR465" s="12"/>
       <c r="AS465" s="12"/>
@@ -69409,7 +69845,7 @@
       <c r="AM466" s="12"/>
       <c r="AN466" s="12"/>
       <c r="AO466" s="39"/>
-      <c r="AP466" s="69"/>
+      <c r="AP466" s="71"/>
       <c r="AQ466" s="12"/>
       <c r="AR466" s="12"/>
       <c r="AS466" s="12"/>
@@ -69472,7 +69908,7 @@
       <c r="AM467" s="12"/>
       <c r="AN467" s="12"/>
       <c r="AO467" s="39"/>
-      <c r="AP467" s="69"/>
+      <c r="AP467" s="71"/>
       <c r="AQ467" s="12"/>
       <c r="AR467" s="12"/>
       <c r="AS467" s="12"/>
@@ -69535,7 +69971,7 @@
       <c r="AM468" s="12"/>
       <c r="AN468" s="12"/>
       <c r="AO468" s="39"/>
-      <c r="AP468" s="69"/>
+      <c r="AP468" s="71"/>
       <c r="AQ468" s="12"/>
       <c r="AR468" s="12"/>
       <c r="AS468" s="12"/>
@@ -69598,7 +70034,7 @@
       <c r="AM469" s="12"/>
       <c r="AN469" s="12"/>
       <c r="AO469" s="39"/>
-      <c r="AP469" s="69"/>
+      <c r="AP469" s="71"/>
       <c r="AQ469" s="12"/>
       <c r="AR469" s="12"/>
       <c r="AS469" s="12"/>
@@ -69661,7 +70097,7 @@
       <c r="AM470" s="12"/>
       <c r="AN470" s="12"/>
       <c r="AO470" s="39"/>
-      <c r="AP470" s="69"/>
+      <c r="AP470" s="71"/>
       <c r="AQ470" s="12"/>
       <c r="AR470" s="12"/>
       <c r="AS470" s="12"/>
@@ -69724,7 +70160,7 @@
       <c r="AM471" s="12"/>
       <c r="AN471" s="12"/>
       <c r="AO471" s="39"/>
-      <c r="AP471" s="69"/>
+      <c r="AP471" s="71"/>
       <c r="AQ471" s="12"/>
       <c r="AR471" s="12"/>
       <c r="AS471" s="12"/>
@@ -69787,7 +70223,7 @@
       <c r="AM472" s="12"/>
       <c r="AN472" s="12"/>
       <c r="AO472" s="39"/>
-      <c r="AP472" s="69"/>
+      <c r="AP472" s="71"/>
       <c r="AQ472" s="12"/>
       <c r="AR472" s="12"/>
       <c r="AS472" s="12"/>
@@ -69850,7 +70286,7 @@
       <c r="AM473" s="12"/>
       <c r="AN473" s="12"/>
       <c r="AO473" s="39"/>
-      <c r="AP473" s="69"/>
+      <c r="AP473" s="71"/>
       <c r="AQ473" s="12"/>
       <c r="AR473" s="12"/>
       <c r="AS473" s="12"/>
@@ -69913,7 +70349,7 @@
       <c r="AM474" s="12"/>
       <c r="AN474" s="12"/>
       <c r="AO474" s="39"/>
-      <c r="AP474" s="69"/>
+      <c r="AP474" s="71"/>
       <c r="AQ474" s="12"/>
       <c r="AR474" s="12"/>
       <c r="AS474" s="12"/>
@@ -69976,7 +70412,7 @@
       <c r="AM475" s="12"/>
       <c r="AN475" s="12"/>
       <c r="AO475" s="39"/>
-      <c r="AP475" s="69"/>
+      <c r="AP475" s="71"/>
       <c r="AQ475" s="12"/>
       <c r="AR475" s="12"/>
       <c r="AS475" s="12"/>
@@ -70039,7 +70475,7 @@
       <c r="AM476" s="12"/>
       <c r="AN476" s="12"/>
       <c r="AO476" s="39"/>
-      <c r="AP476" s="69"/>
+      <c r="AP476" s="71"/>
       <c r="AQ476" s="12"/>
       <c r="AR476" s="12"/>
       <c r="AS476" s="12"/>
@@ -70102,7 +70538,7 @@
       <c r="AM477" s="12"/>
       <c r="AN477" s="12"/>
       <c r="AO477" s="39"/>
-      <c r="AP477" s="69"/>
+      <c r="AP477" s="71"/>
       <c r="AQ477" s="12"/>
       <c r="AR477" s="12"/>
       <c r="AS477" s="12"/>
@@ -70165,7 +70601,7 @@
       <c r="AM478" s="12"/>
       <c r="AN478" s="12"/>
       <c r="AO478" s="39"/>
-      <c r="AP478" s="69"/>
+      <c r="AP478" s="71"/>
       <c r="AQ478" s="12"/>
       <c r="AR478" s="12"/>
       <c r="AS478" s="12"/>
@@ -70228,7 +70664,7 @@
       <c r="AM479" s="12"/>
       <c r="AN479" s="12"/>
       <c r="AO479" s="39"/>
-      <c r="AP479" s="69"/>
+      <c r="AP479" s="71"/>
       <c r="AQ479" s="12"/>
       <c r="AR479" s="12"/>
       <c r="AS479" s="12"/>
@@ -70291,7 +70727,7 @@
       <c r="AM480" s="12"/>
       <c r="AN480" s="12"/>
       <c r="AO480" s="39"/>
-      <c r="AP480" s="69"/>
+      <c r="AP480" s="71"/>
       <c r="AQ480" s="12"/>
       <c r="AR480" s="12"/>
       <c r="AS480" s="12"/>
@@ -70354,7 +70790,7 @@
       <c r="AM481" s="12"/>
       <c r="AN481" s="12"/>
       <c r="AO481" s="39"/>
-      <c r="AP481" s="69"/>
+      <c r="AP481" s="71"/>
       <c r="AQ481" s="12"/>
       <c r="AR481" s="12"/>
       <c r="AS481" s="12"/>
@@ -70417,7 +70853,7 @@
       <c r="AM482" s="12"/>
       <c r="AN482" s="12"/>
       <c r="AO482" s="39"/>
-      <c r="AP482" s="69"/>
+      <c r="AP482" s="71"/>
       <c r="AQ482" s="12"/>
       <c r="AR482" s="12"/>
       <c r="AS482" s="12"/>
@@ -70480,7 +70916,7 @@
       <c r="AM483" s="12"/>
       <c r="AN483" s="12"/>
       <c r="AO483" s="39"/>
-      <c r="AP483" s="69"/>
+      <c r="AP483" s="71"/>
       <c r="AQ483" s="12"/>
       <c r="AR483" s="12"/>
       <c r="AS483" s="12"/>
@@ -70543,7 +70979,7 @@
       <c r="AM484" s="12"/>
       <c r="AN484" s="12"/>
       <c r="AO484" s="39"/>
-      <c r="AP484" s="69"/>
+      <c r="AP484" s="71"/>
       <c r="AQ484" s="12"/>
       <c r="AR484" s="12"/>
       <c r="AS484" s="12"/>
@@ -70606,7 +71042,7 @@
       <c r="AM485" s="12"/>
       <c r="AN485" s="12"/>
       <c r="AO485" s="39"/>
-      <c r="AP485" s="69"/>
+      <c r="AP485" s="71"/>
       <c r="AQ485" s="12"/>
       <c r="AR485" s="12"/>
       <c r="AS485" s="12"/>
@@ -70669,7 +71105,7 @@
       <c r="AM486" s="12"/>
       <c r="AN486" s="12"/>
       <c r="AO486" s="39"/>
-      <c r="AP486" s="69"/>
+      <c r="AP486" s="71"/>
       <c r="AQ486" s="12"/>
       <c r="AR486" s="12"/>
       <c r="AS486" s="12"/>
@@ -70732,7 +71168,7 @@
       <c r="AM487" s="12"/>
       <c r="AN487" s="12"/>
       <c r="AO487" s="39"/>
-      <c r="AP487" s="69"/>
+      <c r="AP487" s="71"/>
       <c r="AQ487" s="12"/>
       <c r="AR487" s="12"/>
       <c r="AS487" s="12"/>
@@ -70795,7 +71231,7 @@
       <c r="AM488" s="12"/>
       <c r="AN488" s="12"/>
       <c r="AO488" s="39"/>
-      <c r="AP488" s="69"/>
+      <c r="AP488" s="71"/>
       <c r="AQ488" s="12"/>
       <c r="AR488" s="12"/>
       <c r="AS488" s="12"/>
@@ -70858,7 +71294,7 @@
       <c r="AM489" s="12"/>
       <c r="AN489" s="12"/>
       <c r="AO489" s="39"/>
-      <c r="AP489" s="69"/>
+      <c r="AP489" s="71"/>
       <c r="AQ489" s="12"/>
       <c r="AR489" s="12"/>
       <c r="AS489" s="12"/>
@@ -70921,7 +71357,7 @@
       <c r="AM490" s="12"/>
       <c r="AN490" s="12"/>
       <c r="AO490" s="39"/>
-      <c r="AP490" s="69"/>
+      <c r="AP490" s="71"/>
       <c r="AQ490" s="12"/>
       <c r="AR490" s="12"/>
       <c r="AS490" s="12"/>
@@ -70984,7 +71420,7 @@
       <c r="AM491" s="12"/>
       <c r="AN491" s="12"/>
       <c r="AO491" s="39"/>
-      <c r="AP491" s="69"/>
+      <c r="AP491" s="71"/>
       <c r="AQ491" s="12"/>
       <c r="AR491" s="12"/>
       <c r="AS491" s="12"/>
@@ -71047,7 +71483,7 @@
       <c r="AM492" s="12"/>
       <c r="AN492" s="12"/>
       <c r="AO492" s="39"/>
-      <c r="AP492" s="69"/>
+      <c r="AP492" s="71"/>
       <c r="AQ492" s="12"/>
       <c r="AR492" s="12"/>
       <c r="AS492" s="12"/>
@@ -71110,7 +71546,7 @@
       <c r="AM493" s="12"/>
       <c r="AN493" s="12"/>
       <c r="AO493" s="39"/>
-      <c r="AP493" s="69"/>
+      <c r="AP493" s="71"/>
       <c r="AQ493" s="12"/>
       <c r="AR493" s="12"/>
       <c r="AS493" s="12"/>
@@ -71173,7 +71609,7 @@
       <c r="AM494" s="12"/>
       <c r="AN494" s="12"/>
       <c r="AO494" s="39"/>
-      <c r="AP494" s="69"/>
+      <c r="AP494" s="71"/>
       <c r="AQ494" s="12"/>
       <c r="AR494" s="12"/>
       <c r="AS494" s="12"/>
@@ -71236,7 +71672,7 @@
       <c r="AM495" s="12"/>
       <c r="AN495" s="12"/>
       <c r="AO495" s="39"/>
-      <c r="AP495" s="69"/>
+      <c r="AP495" s="71"/>
       <c r="AQ495" s="12"/>
       <c r="AR495" s="12"/>
       <c r="AS495" s="12"/>
@@ -71299,7 +71735,7 @@
       <c r="AM496" s="12"/>
       <c r="AN496" s="12"/>
       <c r="AO496" s="39"/>
-      <c r="AP496" s="69"/>
+      <c r="AP496" s="71"/>
       <c r="AQ496" s="12"/>
       <c r="AR496" s="12"/>
       <c r="AS496" s="12"/>
@@ -71362,7 +71798,7 @@
       <c r="AM497" s="12"/>
       <c r="AN497" s="12"/>
       <c r="AO497" s="39"/>
-      <c r="AP497" s="69"/>
+      <c r="AP497" s="71"/>
       <c r="AQ497" s="12"/>
       <c r="AR497" s="12"/>
       <c r="AS497" s="12"/>
@@ -71425,7 +71861,7 @@
       <c r="AM498" s="12"/>
       <c r="AN498" s="12"/>
       <c r="AO498" s="39"/>
-      <c r="AP498" s="69"/>
+      <c r="AP498" s="71"/>
       <c r="AQ498" s="12"/>
       <c r="AR498" s="12"/>
       <c r="AS498" s="12"/>
@@ -71488,7 +71924,7 @@
       <c r="AM499" s="12"/>
       <c r="AN499" s="12"/>
       <c r="AO499" s="39"/>
-      <c r="AP499" s="69"/>
+      <c r="AP499" s="71"/>
       <c r="AQ499" s="12"/>
       <c r="AR499" s="12"/>
       <c r="AS499" s="12"/>
@@ -71551,7 +71987,7 @@
       <c r="AM500" s="12"/>
       <c r="AN500" s="12"/>
       <c r="AO500" s="39"/>
-      <c r="AP500" s="69"/>
+      <c r="AP500" s="71"/>
       <c r="AQ500" s="12"/>
       <c r="AR500" s="12"/>
       <c r="AS500" s="12"/>
@@ -71614,7 +72050,7 @@
       <c r="AM501" s="12"/>
       <c r="AN501" s="12"/>
       <c r="AO501" s="39"/>
-      <c r="AP501" s="69"/>
+      <c r="AP501" s="71"/>
       <c r="AQ501" s="12"/>
       <c r="AR501" s="12"/>
       <c r="AS501" s="12"/>
@@ -71677,7 +72113,7 @@
       <c r="AM502" s="12"/>
       <c r="AN502" s="12"/>
       <c r="AO502" s="39"/>
-      <c r="AP502" s="69"/>
+      <c r="AP502" s="71"/>
       <c r="AQ502" s="12"/>
       <c r="AR502" s="12"/>
       <c r="AS502" s="12"/>
@@ -71740,7 +72176,7 @@
       <c r="AM503" s="12"/>
       <c r="AN503" s="12"/>
       <c r="AO503" s="39"/>
-      <c r="AP503" s="69"/>
+      <c r="AP503" s="71"/>
       <c r="AQ503" s="12"/>
       <c r="AR503" s="12"/>
       <c r="AS503" s="12"/>
@@ -71803,7 +72239,7 @@
       <c r="AM504" s="12"/>
       <c r="AN504" s="12"/>
       <c r="AO504" s="39"/>
-      <c r="AP504" s="69"/>
+      <c r="AP504" s="71"/>
       <c r="AQ504" s="12"/>
       <c r="AR504" s="12"/>
       <c r="AS504" s="12"/>
@@ -71866,7 +72302,7 @@
       <c r="AM505" s="12"/>
       <c r="AN505" s="12"/>
       <c r="AO505" s="39"/>
-      <c r="AP505" s="69"/>
+      <c r="AP505" s="71"/>
       <c r="AQ505" s="12"/>
       <c r="AR505" s="12"/>
       <c r="AS505" s="12"/>
@@ -71929,7 +72365,7 @@
       <c r="AM506" s="12"/>
       <c r="AN506" s="12"/>
       <c r="AO506" s="39"/>
-      <c r="AP506" s="69"/>
+      <c r="AP506" s="71"/>
       <c r="AQ506" s="12"/>
       <c r="AR506" s="12"/>
       <c r="AS506" s="12"/>
@@ -71992,7 +72428,7 @@
       <c r="AM507" s="12"/>
       <c r="AN507" s="12"/>
       <c r="AO507" s="39"/>
-      <c r="AP507" s="69"/>
+      <c r="AP507" s="71"/>
       <c r="AQ507" s="12"/>
       <c r="AR507" s="12"/>
       <c r="AS507" s="12"/>
@@ -72055,7 +72491,7 @@
       <c r="AM508" s="12"/>
       <c r="AN508" s="12"/>
       <c r="AO508" s="39"/>
-      <c r="AP508" s="69"/>
+      <c r="AP508" s="71"/>
       <c r="AQ508" s="12"/>
       <c r="AR508" s="12"/>
       <c r="AS508" s="12"/>
@@ -72118,7 +72554,7 @@
       <c r="AM509" s="12"/>
       <c r="AN509" s="12"/>
       <c r="AO509" s="39"/>
-      <c r="AP509" s="69"/>
+      <c r="AP509" s="71"/>
       <c r="AQ509" s="12"/>
       <c r="AR509" s="12"/>
       <c r="AS509" s="12"/>
@@ -72181,7 +72617,7 @@
       <c r="AM510" s="12"/>
       <c r="AN510" s="12"/>
       <c r="AO510" s="39"/>
-      <c r="AP510" s="69"/>
+      <c r="AP510" s="71"/>
       <c r="AQ510" s="12"/>
       <c r="AR510" s="12"/>
       <c r="AS510" s="12"/>
@@ -72244,7 +72680,7 @@
       <c r="AM511" s="12"/>
       <c r="AN511" s="12"/>
       <c r="AO511" s="39"/>
-      <c r="AP511" s="69"/>
+      <c r="AP511" s="71"/>
       <c r="AQ511" s="12"/>
       <c r="AR511" s="12"/>
       <c r="AS511" s="12"/>
@@ -72307,7 +72743,7 @@
       <c r="AM512" s="12"/>
       <c r="AN512" s="12"/>
       <c r="AO512" s="39"/>
-      <c r="AP512" s="69"/>
+      <c r="AP512" s="71"/>
       <c r="AQ512" s="12"/>
       <c r="AR512" s="12"/>
       <c r="AS512" s="12"/>
@@ -72370,7 +72806,7 @@
       <c r="AM513" s="12"/>
       <c r="AN513" s="12"/>
       <c r="AO513" s="39"/>
-      <c r="AP513" s="69"/>
+      <c r="AP513" s="71"/>
       <c r="AQ513" s="12"/>
       <c r="AR513" s="12"/>
       <c r="AS513" s="12"/>
@@ -72433,7 +72869,7 @@
       <c r="AM514" s="12"/>
       <c r="AN514" s="12"/>
       <c r="AO514" s="39"/>
-      <c r="AP514" s="69"/>
+      <c r="AP514" s="71"/>
       <c r="AQ514" s="12"/>
       <c r="AR514" s="12"/>
       <c r="AS514" s="12"/>
@@ -72496,7 +72932,7 @@
       <c r="AM515" s="12"/>
       <c r="AN515" s="12"/>
       <c r="AO515" s="39"/>
-      <c r="AP515" s="69"/>
+      <c r="AP515" s="71"/>
       <c r="AQ515" s="12"/>
       <c r="AR515" s="12"/>
       <c r="AS515" s="12"/>
@@ -72559,7 +72995,7 @@
       <c r="AM516" s="12"/>
       <c r="AN516" s="12"/>
       <c r="AO516" s="39"/>
-      <c r="AP516" s="69"/>
+      <c r="AP516" s="71"/>
       <c r="AQ516" s="12"/>
       <c r="AR516" s="12"/>
       <c r="AS516" s="12"/>
@@ -72622,7 +73058,7 @@
       <c r="AM517" s="12"/>
       <c r="AN517" s="12"/>
       <c r="AO517" s="39"/>
-      <c r="AP517" s="69"/>
+      <c r="AP517" s="71"/>
       <c r="AQ517" s="12"/>
       <c r="AR517" s="12"/>
       <c r="AS517" s="12"/>
@@ -72685,7 +73121,7 @@
       <c r="AM518" s="12"/>
       <c r="AN518" s="12"/>
       <c r="AO518" s="39"/>
-      <c r="AP518" s="69"/>
+      <c r="AP518" s="71"/>
       <c r="AQ518" s="12"/>
       <c r="AR518" s="12"/>
       <c r="AS518" s="12"/>
@@ -72748,7 +73184,7 @@
       <c r="AM519" s="12"/>
       <c r="AN519" s="12"/>
       <c r="AO519" s="39"/>
-      <c r="AP519" s="69"/>
+      <c r="AP519" s="71"/>
       <c r="AQ519" s="12"/>
       <c r="AR519" s="12"/>
       <c r="AS519" s="12"/>
@@ -72811,7 +73247,7 @@
       <c r="AM520" s="12"/>
       <c r="AN520" s="12"/>
       <c r="AO520" s="39"/>
-      <c r="AP520" s="69"/>
+      <c r="AP520" s="71"/>
       <c r="AQ520" s="12"/>
       <c r="AR520" s="12"/>
       <c r="AS520" s="12"/>
@@ -72874,7 +73310,7 @@
       <c r="AM521" s="12"/>
       <c r="AN521" s="12"/>
       <c r="AO521" s="39"/>
-      <c r="AP521" s="69"/>
+      <c r="AP521" s="71"/>
       <c r="AQ521" s="12"/>
       <c r="AR521" s="12"/>
       <c r="AS521" s="12"/>
@@ -72937,7 +73373,7 @@
       <c r="AM522" s="12"/>
       <c r="AN522" s="12"/>
       <c r="AO522" s="39"/>
-      <c r="AP522" s="69"/>
+      <c r="AP522" s="71"/>
       <c r="AQ522" s="12"/>
       <c r="AR522" s="12"/>
       <c r="AS522" s="12"/>
@@ -73000,7 +73436,7 @@
       <c r="AM523" s="12"/>
       <c r="AN523" s="12"/>
       <c r="AO523" s="39"/>
-      <c r="AP523" s="69"/>
+      <c r="AP523" s="71"/>
       <c r="AQ523" s="12"/>
       <c r="AR523" s="12"/>
       <c r="AS523" s="12"/>
@@ -73063,7 +73499,7 @@
       <c r="AM524" s="12"/>
       <c r="AN524" s="12"/>
       <c r="AO524" s="39"/>
-      <c r="AP524" s="69"/>
+      <c r="AP524" s="71"/>
       <c r="AQ524" s="12"/>
       <c r="AR524" s="12"/>
       <c r="AS524" s="12"/>
@@ -73126,7 +73562,7 @@
       <c r="AM525" s="12"/>
       <c r="AN525" s="12"/>
       <c r="AO525" s="39"/>
-      <c r="AP525" s="69"/>
+      <c r="AP525" s="71"/>
       <c r="AQ525" s="12"/>
       <c r="AR525" s="12"/>
       <c r="AS525" s="12"/>
@@ -73189,7 +73625,7 @@
       <c r="AM526" s="12"/>
       <c r="AN526" s="12"/>
       <c r="AO526" s="39"/>
-      <c r="AP526" s="69"/>
+      <c r="AP526" s="71"/>
       <c r="AQ526" s="12"/>
       <c r="AR526" s="12"/>
       <c r="AS526" s="12"/>
@@ -73252,7 +73688,7 @@
       <c r="AM527" s="12"/>
       <c r="AN527" s="12"/>
       <c r="AO527" s="39"/>
-      <c r="AP527" s="69"/>
+      <c r="AP527" s="71"/>
       <c r="AQ527" s="12"/>
       <c r="AR527" s="12"/>
       <c r="AS527" s="12"/>
@@ -73315,7 +73751,7 @@
       <c r="AM528" s="12"/>
       <c r="AN528" s="12"/>
       <c r="AO528" s="39"/>
-      <c r="AP528" s="69"/>
+      <c r="AP528" s="71"/>
       <c r="AQ528" s="12"/>
       <c r="AR528" s="12"/>
       <c r="AS528" s="12"/>
@@ -73378,7 +73814,7 @@
       <c r="AM529" s="12"/>
       <c r="AN529" s="12"/>
       <c r="AO529" s="39"/>
-      <c r="AP529" s="69"/>
+      <c r="AP529" s="71"/>
       <c r="AQ529" s="12"/>
       <c r="AR529" s="12"/>
       <c r="AS529" s="12"/>
@@ -73441,7 +73877,7 @@
       <c r="AM530" s="12"/>
       <c r="AN530" s="12"/>
       <c r="AO530" s="39"/>
-      <c r="AP530" s="69"/>
+      <c r="AP530" s="71"/>
       <c r="AQ530" s="12"/>
       <c r="AR530" s="12"/>
       <c r="AS530" s="12"/>
@@ -73504,7 +73940,7 @@
       <c r="AM531" s="12"/>
       <c r="AN531" s="12"/>
       <c r="AO531" s="39"/>
-      <c r="AP531" s="69"/>
+      <c r="AP531" s="71"/>
       <c r="AQ531" s="12"/>
       <c r="AR531" s="12"/>
       <c r="AS531" s="12"/>
@@ -73567,7 +74003,7 @@
       <c r="AM532" s="12"/>
       <c r="AN532" s="12"/>
       <c r="AO532" s="39"/>
-      <c r="AP532" s="69"/>
+      <c r="AP532" s="71"/>
       <c r="AQ532" s="12"/>
       <c r="AR532" s="12"/>
       <c r="AS532" s="12"/>
@@ -73630,7 +74066,7 @@
       <c r="AM533" s="12"/>
       <c r="AN533" s="12"/>
       <c r="AO533" s="39"/>
-      <c r="AP533" s="69"/>
+      <c r="AP533" s="71"/>
       <c r="AQ533" s="12"/>
       <c r="AR533" s="12"/>
       <c r="AS533" s="12"/>
@@ -73693,7 +74129,7 @@
       <c r="AM534" s="12"/>
       <c r="AN534" s="12"/>
       <c r="AO534" s="39"/>
-      <c r="AP534" s="69"/>
+      <c r="AP534" s="71"/>
       <c r="AQ534" s="12"/>
       <c r="AR534" s="12"/>
       <c r="AS534" s="12"/>
@@ -73756,7 +74192,7 @@
       <c r="AM535" s="12"/>
       <c r="AN535" s="12"/>
       <c r="AO535" s="39"/>
-      <c r="AP535" s="69"/>
+      <c r="AP535" s="71"/>
       <c r="AQ535" s="12"/>
       <c r="AR535" s="12"/>
       <c r="AS535" s="12"/>
@@ -73819,7 +74255,7 @@
       <c r="AM536" s="12"/>
       <c r="AN536" s="12"/>
       <c r="AO536" s="39"/>
-      <c r="AP536" s="69"/>
+      <c r="AP536" s="71"/>
       <c r="AQ536" s="12"/>
       <c r="AR536" s="12"/>
       <c r="AS536" s="12"/>
@@ -73882,7 +74318,7 @@
       <c r="AM537" s="12"/>
       <c r="AN537" s="12"/>
       <c r="AO537" s="39"/>
-      <c r="AP537" s="69"/>
+      <c r="AP537" s="71"/>
       <c r="AQ537" s="12"/>
       <c r="AR537" s="12"/>
       <c r="AS537" s="12"/>
@@ -73945,7 +74381,7 @@
       <c r="AM538" s="12"/>
       <c r="AN538" s="12"/>
       <c r="AO538" s="39"/>
-      <c r="AP538" s="69"/>
+      <c r="AP538" s="71"/>
       <c r="AQ538" s="12"/>
       <c r="AR538" s="12"/>
       <c r="AS538" s="12"/>
@@ -74008,7 +74444,7 @@
       <c r="AM539" s="12"/>
       <c r="AN539" s="12"/>
       <c r="AO539" s="39"/>
-      <c r="AP539" s="69"/>
+      <c r="AP539" s="71"/>
       <c r="AQ539" s="12"/>
       <c r="AR539" s="12"/>
       <c r="AS539" s="12"/>
@@ -74071,7 +74507,7 @@
       <c r="AM540" s="12"/>
       <c r="AN540" s="12"/>
       <c r="AO540" s="39"/>
-      <c r="AP540" s="69"/>
+      <c r="AP540" s="71"/>
       <c r="AQ540" s="12"/>
       <c r="AR540" s="12"/>
       <c r="AS540" s="12"/>
@@ -74134,7 +74570,7 @@
       <c r="AM541" s="12"/>
       <c r="AN541" s="12"/>
       <c r="AO541" s="39"/>
-      <c r="AP541" s="69"/>
+      <c r="AP541" s="71"/>
       <c r="AQ541" s="12"/>
       <c r="AR541" s="12"/>
       <c r="AS541" s="12"/>
@@ -74197,7 +74633,7 @@
       <c r="AM542" s="12"/>
       <c r="AN542" s="12"/>
       <c r="AO542" s="39"/>
-      <c r="AP542" s="69"/>
+      <c r="AP542" s="71"/>
       <c r="AQ542" s="12"/>
       <c r="AR542" s="12"/>
       <c r="AS542" s="12"/>
@@ -74260,7 +74696,7 @@
       <c r="AM543" s="12"/>
       <c r="AN543" s="12"/>
       <c r="AO543" s="39"/>
-      <c r="AP543" s="69"/>
+      <c r="AP543" s="71"/>
       <c r="AQ543" s="12"/>
       <c r="AR543" s="12"/>
       <c r="AS543" s="12"/>
@@ -74323,7 +74759,7 @@
       <c r="AM544" s="12"/>
       <c r="AN544" s="12"/>
       <c r="AO544" s="39"/>
-      <c r="AP544" s="69"/>
+      <c r="AP544" s="71"/>
       <c r="AQ544" s="12"/>
       <c r="AR544" s="12"/>
       <c r="AS544" s="12"/>
@@ -74386,7 +74822,7 @@
       <c r="AM545" s="12"/>
       <c r="AN545" s="12"/>
       <c r="AO545" s="39"/>
-      <c r="AP545" s="69"/>
+      <c r="AP545" s="71"/>
       <c r="AQ545" s="12"/>
       <c r="AR545" s="12"/>
       <c r="AS545" s="12"/>
@@ -74449,7 +74885,7 @@
       <c r="AM546" s="12"/>
       <c r="AN546" s="12"/>
       <c r="AO546" s="39"/>
-      <c r="AP546" s="69"/>
+      <c r="AP546" s="71"/>
       <c r="AQ546" s="12"/>
       <c r="AR546" s="12"/>
       <c r="AS546" s="12"/>
@@ -74512,7 +74948,7 @@
       <c r="AM547" s="12"/>
       <c r="AN547" s="12"/>
       <c r="AO547" s="39"/>
-      <c r="AP547" s="69"/>
+      <c r="AP547" s="71"/>
       <c r="AQ547" s="12"/>
       <c r="AR547" s="12"/>
       <c r="AS547" s="12"/>
@@ -74575,7 +75011,7 @@
       <c r="AM548" s="12"/>
       <c r="AN548" s="12"/>
       <c r="AO548" s="39"/>
-      <c r="AP548" s="69"/>
+      <c r="AP548" s="71"/>
       <c r="AQ548" s="12"/>
       <c r="AR548" s="12"/>
       <c r="AS548" s="12"/>
@@ -74638,7 +75074,7 @@
       <c r="AM549" s="12"/>
       <c r="AN549" s="12"/>
       <c r="AO549" s="39"/>
-      <c r="AP549" s="69"/>
+      <c r="AP549" s="71"/>
       <c r="AQ549" s="12"/>
       <c r="AR549" s="12"/>
       <c r="AS549" s="12"/>
@@ -74701,7 +75137,7 @@
       <c r="AM550" s="12"/>
       <c r="AN550" s="12"/>
       <c r="AO550" s="39"/>
-      <c r="AP550" s="69"/>
+      <c r="AP550" s="71"/>
       <c r="AQ550" s="12"/>
       <c r="AR550" s="12"/>
       <c r="AS550" s="12"/>
@@ -74764,7 +75200,7 @@
       <c r="AM551" s="12"/>
       <c r="AN551" s="12"/>
       <c r="AO551" s="39"/>
-      <c r="AP551" s="69"/>
+      <c r="AP551" s="71"/>
       <c r="AQ551" s="12"/>
       <c r="AR551" s="12"/>
       <c r="AS551" s="12"/>
@@ -74827,7 +75263,7 @@
       <c r="AM552" s="12"/>
       <c r="AN552" s="12"/>
       <c r="AO552" s="39"/>
-      <c r="AP552" s="69"/>
+      <c r="AP552" s="71"/>
       <c r="AQ552" s="12"/>
       <c r="AR552" s="12"/>
       <c r="AS552" s="12"/>
@@ -74890,7 +75326,7 @@
       <c r="AM553" s="12"/>
       <c r="AN553" s="12"/>
       <c r="AO553" s="39"/>
-      <c r="AP553" s="69"/>
+      <c r="AP553" s="71"/>
       <c r="AQ553" s="12"/>
       <c r="AR553" s="12"/>
       <c r="AS553" s="12"/>
@@ -74953,7 +75389,7 @@
       <c r="AM554" s="12"/>
       <c r="AN554" s="12"/>
       <c r="AO554" s="39"/>
-      <c r="AP554" s="69"/>
+      <c r="AP554" s="71"/>
       <c r="AQ554" s="12"/>
       <c r="AR554" s="12"/>
       <c r="AS554" s="12"/>
@@ -75016,7 +75452,7 @@
       <c r="AM555" s="12"/>
       <c r="AN555" s="12"/>
       <c r="AO555" s="39"/>
-      <c r="AP555" s="69"/>
+      <c r="AP555" s="71"/>
       <c r="AQ555" s="12"/>
       <c r="AR555" s="12"/>
       <c r="AS555" s="12"/>
@@ -75079,7 +75515,7 @@
       <c r="AM556" s="12"/>
       <c r="AN556" s="12"/>
       <c r="AO556" s="39"/>
-      <c r="AP556" s="69"/>
+      <c r="AP556" s="71"/>
       <c r="AQ556" s="12"/>
       <c r="AR556" s="12"/>
       <c r="AS556" s="12"/>
@@ -75142,7 +75578,7 @@
       <c r="AM557" s="12"/>
       <c r="AN557" s="12"/>
       <c r="AO557" s="39"/>
-      <c r="AP557" s="69"/>
+      <c r="AP557" s="71"/>
       <c r="AQ557" s="12"/>
       <c r="AR557" s="12"/>
       <c r="AS557" s="12"/>
@@ -75205,7 +75641,7 @@
       <c r="AM558" s="12"/>
       <c r="AN558" s="12"/>
       <c r="AO558" s="39"/>
-      <c r="AP558" s="69"/>
+      <c r="AP558" s="71"/>
       <c r="AQ558" s="12"/>
       <c r="AR558" s="12"/>
       <c r="AS558" s="12"/>
@@ -75268,7 +75704,7 @@
       <c r="AM559" s="12"/>
       <c r="AN559" s="12"/>
       <c r="AO559" s="39"/>
-      <c r="AP559" s="69"/>
+      <c r="AP559" s="71"/>
       <c r="AQ559" s="12"/>
       <c r="AR559" s="12"/>
       <c r="AS559" s="12"/>
@@ -75331,7 +75767,7 @@
       <c r="AM560" s="12"/>
       <c r="AN560" s="12"/>
       <c r="AO560" s="39"/>
-      <c r="AP560" s="69"/>
+      <c r="AP560" s="71"/>
       <c r="AQ560" s="12"/>
       <c r="AR560" s="12"/>
       <c r="AS560" s="12"/>
@@ -75394,7 +75830,7 @@
       <c r="AM561" s="12"/>
       <c r="AN561" s="12"/>
       <c r="AO561" s="39"/>
-      <c r="AP561" s="69"/>
+      <c r="AP561" s="71"/>
       <c r="AQ561" s="12"/>
       <c r="AR561" s="12"/>
       <c r="AS561" s="12"/>
@@ -75457,7 +75893,7 @@
       <c r="AM562" s="12"/>
       <c r="AN562" s="12"/>
       <c r="AO562" s="39"/>
-      <c r="AP562" s="69"/>
+      <c r="AP562" s="71"/>
       <c r="AQ562" s="12"/>
       <c r="AR562" s="12"/>
       <c r="AS562" s="12"/>
@@ -75520,7 +75956,7 @@
       <c r="AM563" s="12"/>
       <c r="AN563" s="12"/>
       <c r="AO563" s="39"/>
-      <c r="AP563" s="69"/>
+      <c r="AP563" s="71"/>
       <c r="AQ563" s="12"/>
       <c r="AR563" s="12"/>
       <c r="AS563" s="12"/>
@@ -75583,7 +76019,7 @@
       <c r="AM564" s="12"/>
       <c r="AN564" s="12"/>
       <c r="AO564" s="39"/>
-      <c r="AP564" s="69"/>
+      <c r="AP564" s="71"/>
       <c r="AQ564" s="12"/>
       <c r="AR564" s="12"/>
       <c r="AS564" s="12"/>
@@ -75646,7 +76082,7 @@
       <c r="AM565" s="12"/>
       <c r="AN565" s="12"/>
       <c r="AO565" s="39"/>
-      <c r="AP565" s="69"/>
+      <c r="AP565" s="71"/>
       <c r="AQ565" s="12"/>
       <c r="AR565" s="12"/>
       <c r="AS565" s="12"/>
@@ -75709,7 +76145,7 @@
       <c r="AM566" s="12"/>
       <c r="AN566" s="12"/>
       <c r="AO566" s="39"/>
-      <c r="AP566" s="69"/>
+      <c r="AP566" s="71"/>
       <c r="AQ566" s="12"/>
       <c r="AR566" s="12"/>
       <c r="AS566" s="12"/>
@@ -75772,7 +76208,7 @@
       <c r="AM567" s="12"/>
       <c r="AN567" s="12"/>
       <c r="AO567" s="39"/>
-      <c r="AP567" s="69"/>
+      <c r="AP567" s="71"/>
       <c r="AQ567" s="12"/>
       <c r="AR567" s="12"/>
       <c r="AS567" s="12"/>
@@ -75835,7 +76271,7 @@
       <c r="AM568" s="12"/>
       <c r="AN568" s="12"/>
       <c r="AO568" s="39"/>
-      <c r="AP568" s="69"/>
+      <c r="AP568" s="71"/>
       <c r="AQ568" s="12"/>
       <c r="AR568" s="12"/>
       <c r="AS568" s="12"/>
@@ -75898,7 +76334,7 @@
       <c r="AM569" s="12"/>
       <c r="AN569" s="12"/>
       <c r="AO569" s="39"/>
-      <c r="AP569" s="69"/>
+      <c r="AP569" s="71"/>
       <c r="AQ569" s="12"/>
       <c r="AR569" s="12"/>
       <c r="AS569" s="12"/>
@@ -75961,7 +76397,7 @@
       <c r="AM570" s="12"/>
       <c r="AN570" s="12"/>
       <c r="AO570" s="39"/>
-      <c r="AP570" s="69"/>
+      <c r="AP570" s="71"/>
       <c r="AQ570" s="12"/>
       <c r="AR570" s="12"/>
       <c r="AS570" s="12"/>
@@ -76024,7 +76460,7 @@
       <c r="AM571" s="12"/>
       <c r="AN571" s="12"/>
       <c r="AO571" s="39"/>
-      <c r="AP571" s="69"/>
+      <c r="AP571" s="71"/>
       <c r="AQ571" s="12"/>
       <c r="AR571" s="12"/>
       <c r="AS571" s="12"/>
@@ -76087,7 +76523,7 @@
       <c r="AM572" s="12"/>
       <c r="AN572" s="12"/>
       <c r="AO572" s="39"/>
-      <c r="AP572" s="69"/>
+      <c r="AP572" s="71"/>
       <c r="AQ572" s="12"/>
       <c r="AR572" s="12"/>
       <c r="AS572" s="12"/>
@@ -76150,7 +76586,7 @@
       <c r="AM573" s="12"/>
       <c r="AN573" s="12"/>
       <c r="AO573" s="39"/>
-      <c r="AP573" s="69"/>
+      <c r="AP573" s="71"/>
       <c r="AQ573" s="12"/>
       <c r="AR573" s="12"/>
       <c r="AS573" s="12"/>
@@ -76213,7 +76649,7 @@
       <c r="AM574" s="12"/>
       <c r="AN574" s="12"/>
       <c r="AO574" s="39"/>
-      <c r="AP574" s="69"/>
+      <c r="AP574" s="71"/>
       <c r="AQ574" s="12"/>
       <c r="AR574" s="12"/>
       <c r="AS574" s="12"/>
@@ -76276,7 +76712,7 @@
       <c r="AM575" s="12"/>
       <c r="AN575" s="12"/>
       <c r="AO575" s="39"/>
-      <c r="AP575" s="69"/>
+      <c r="AP575" s="71"/>
       <c r="AQ575" s="12"/>
       <c r="AR575" s="12"/>
       <c r="AS575" s="12"/>
@@ -76339,7 +76775,7 @@
       <c r="AM576" s="12"/>
       <c r="AN576" s="12"/>
       <c r="AO576" s="39"/>
-      <c r="AP576" s="69"/>
+      <c r="AP576" s="71"/>
       <c r="AQ576" s="12"/>
       <c r="AR576" s="12"/>
       <c r="AS576" s="12"/>
@@ -76402,7 +76838,7 @@
       <c r="AM577" s="12"/>
       <c r="AN577" s="12"/>
       <c r="AO577" s="39"/>
-      <c r="AP577" s="69"/>
+      <c r="AP577" s="71"/>
       <c r="AQ577" s="12"/>
       <c r="AR577" s="12"/>
       <c r="AS577" s="12"/>
@@ -76465,7 +76901,7 @@
       <c r="AM578" s="12"/>
       <c r="AN578" s="12"/>
       <c r="AO578" s="39"/>
-      <c r="AP578" s="69"/>
+      <c r="AP578" s="71"/>
       <c r="AQ578" s="12"/>
       <c r="AR578" s="12"/>
       <c r="AS578" s="12"/>
@@ -76528,7 +76964,7 @@
       <c r="AM579" s="12"/>
       <c r="AN579" s="12"/>
       <c r="AO579" s="39"/>
-      <c r="AP579" s="69"/>
+      <c r="AP579" s="71"/>
       <c r="AQ579" s="12"/>
       <c r="AR579" s="12"/>
       <c r="AS579" s="12"/>
@@ -76591,7 +77027,7 @@
       <c r="AM580" s="12"/>
       <c r="AN580" s="12"/>
       <c r="AO580" s="39"/>
-      <c r="AP580" s="69"/>
+      <c r="AP580" s="71"/>
       <c r="AQ580" s="12"/>
       <c r="AR580" s="12"/>
       <c r="AS580" s="12"/>
@@ -76654,7 +77090,7 @@
       <c r="AM581" s="12"/>
       <c r="AN581" s="12"/>
       <c r="AO581" s="39"/>
-      <c r="AP581" s="69"/>
+      <c r="AP581" s="71"/>
       <c r="AQ581" s="12"/>
       <c r="AR581" s="12"/>
       <c r="AS581" s="12"/>
@@ -76717,7 +77153,7 @@
       <c r="AM582" s="12"/>
       <c r="AN582" s="12"/>
       <c r="AO582" s="39"/>
-      <c r="AP582" s="69"/>
+      <c r="AP582" s="71"/>
       <c r="AQ582" s="12"/>
       <c r="AR582" s="12"/>
       <c r="AS582" s="12"/>
@@ -76780,7 +77216,7 @@
       <c r="AM583" s="12"/>
       <c r="AN583" s="12"/>
       <c r="AO583" s="39"/>
-      <c r="AP583" s="69"/>
+      <c r="AP583" s="71"/>
       <c r="AQ583" s="12"/>
       <c r="AR583" s="12"/>
       <c r="AS583" s="12"/>
@@ -76843,7 +77279,7 @@
       <c r="AM584" s="12"/>
       <c r="AN584" s="12"/>
       <c r="AO584" s="39"/>
-      <c r="AP584" s="69"/>
+      <c r="AP584" s="71"/>
       <c r="AQ584" s="12"/>
       <c r="AR584" s="12"/>
       <c r="AS584" s="12"/>
@@ -76906,7 +77342,7 @@
       <c r="AM585" s="12"/>
       <c r="AN585" s="12"/>
       <c r="AO585" s="39"/>
-      <c r="AP585" s="69"/>
+      <c r="AP585" s="71"/>
       <c r="AQ585" s="12"/>
       <c r="AR585" s="12"/>
       <c r="AS585" s="12"/>
@@ -76969,7 +77405,7 @@
       <c r="AM586" s="12"/>
       <c r="AN586" s="12"/>
       <c r="AO586" s="39"/>
-      <c r="AP586" s="69"/>
+      <c r="AP586" s="71"/>
       <c r="AQ586" s="12"/>
       <c r="AR586" s="12"/>
       <c r="AS586" s="12"/>
@@ -77032,7 +77468,7 @@
       <c r="AM587" s="12"/>
       <c r="AN587" s="12"/>
       <c r="AO587" s="39"/>
-      <c r="AP587" s="69"/>
+      <c r="AP587" s="71"/>
       <c r="AQ587" s="12"/>
       <c r="AR587" s="12"/>
       <c r="AS587" s="12"/>
@@ -77095,7 +77531,7 @@
       <c r="AM588" s="12"/>
       <c r="AN588" s="12"/>
       <c r="AO588" s="39"/>
-      <c r="AP588" s="69"/>
+      <c r="AP588" s="71"/>
       <c r="AQ588" s="12"/>
       <c r="AR588" s="12"/>
       <c r="AS588" s="12"/>
@@ -77158,7 +77594,7 @@
       <c r="AM589" s="12"/>
       <c r="AN589" s="12"/>
       <c r="AO589" s="39"/>
-      <c r="AP589" s="69"/>
+      <c r="AP589" s="71"/>
       <c r="AQ589" s="12"/>
       <c r="AR589" s="12"/>
       <c r="AS589" s="12"/>
@@ -77221,7 +77657,7 @@
       <c r="AM590" s="12"/>
       <c r="AN590" s="12"/>
       <c r="AO590" s="39"/>
-      <c r="AP590" s="69"/>
+      <c r="AP590" s="71"/>
       <c r="AQ590" s="12"/>
       <c r="AR590" s="12"/>
       <c r="AS590" s="12"/>
@@ -77284,7 +77720,7 @@
       <c r="AM591" s="12"/>
       <c r="AN591" s="12"/>
       <c r="AO591" s="39"/>
-      <c r="AP591" s="69"/>
+      <c r="AP591" s="71"/>
       <c r="AQ591" s="12"/>
       <c r="AR591" s="12"/>
       <c r="AS591" s="12"/>
@@ -77347,7 +77783,7 @@
       <c r="AM592" s="12"/>
       <c r="AN592" s="12"/>
       <c r="AO592" s="39"/>
-      <c r="AP592" s="69"/>
+      <c r="AP592" s="71"/>
       <c r="AQ592" s="12"/>
       <c r="AR592" s="12"/>
       <c r="AS592" s="12"/>
@@ -77410,7 +77846,7 @@
       <c r="AM593" s="12"/>
       <c r="AN593" s="12"/>
       <c r="AO593" s="39"/>
-      <c r="AP593" s="69"/>
+      <c r="AP593" s="71"/>
       <c r="AQ593" s="12"/>
       <c r="AR593" s="12"/>
       <c r="AS593" s="12"/>
@@ -77473,7 +77909,7 @@
       <c r="AM594" s="12"/>
       <c r="AN594" s="12"/>
       <c r="AO594" s="39"/>
-      <c r="AP594" s="69"/>
+      <c r="AP594" s="71"/>
       <c r="AQ594" s="12"/>
       <c r="AR594" s="12"/>
       <c r="AS594" s="12"/>
@@ -77536,7 +77972,7 @@
       <c r="AM595" s="12"/>
       <c r="AN595" s="12"/>
       <c r="AO595" s="39"/>
-      <c r="AP595" s="69"/>
+      <c r="AP595" s="71"/>
       <c r="AQ595" s="12"/>
       <c r="AR595" s="12"/>
       <c r="AS595" s="12"/>
@@ -77599,7 +78035,7 @@
       <c r="AM596" s="12"/>
       <c r="AN596" s="12"/>
       <c r="AO596" s="39"/>
-      <c r="AP596" s="69"/>
+      <c r="AP596" s="71"/>
       <c r="AQ596" s="12"/>
       <c r="AR596" s="12"/>
       <c r="AS596" s="12"/>
@@ -77662,7 +78098,7 @@
       <c r="AM597" s="12"/>
       <c r="AN597" s="12"/>
       <c r="AO597" s="39"/>
-      <c r="AP597" s="69"/>
+      <c r="AP597" s="71"/>
       <c r="AQ597" s="12"/>
       <c r="AR597" s="12"/>
       <c r="AS597" s="12"/>
@@ -77725,7 +78161,7 @@
       <c r="AM598" s="12"/>
       <c r="AN598" s="12"/>
       <c r="AO598" s="39"/>
-      <c r="AP598" s="69"/>
+      <c r="AP598" s="71"/>
       <c r="AQ598" s="12"/>
       <c r="AR598" s="12"/>
       <c r="AS598" s="12"/>
@@ -77788,7 +78224,7 @@
       <c r="AM599" s="12"/>
       <c r="AN599" s="12"/>
       <c r="AO599" s="39"/>
-      <c r="AP599" s="69"/>
+      <c r="AP599" s="71"/>
       <c r="AQ599" s="12"/>
       <c r="AR599" s="12"/>
       <c r="AS599" s="12"/>
@@ -77851,7 +78287,7 @@
       <c r="AM600" s="12"/>
       <c r="AN600" s="12"/>
       <c r="AO600" s="39"/>
-      <c r="AP600" s="69"/>
+      <c r="AP600" s="71"/>
       <c r="AQ600" s="12"/>
       <c r="AR600" s="12"/>
       <c r="AS600" s="12"/>
@@ -77914,7 +78350,7 @@
       <c r="AM601" s="12"/>
       <c r="AN601" s="12"/>
       <c r="AO601" s="39"/>
-      <c r="AP601" s="69"/>
+      <c r="AP601" s="71"/>
       <c r="AQ601" s="12"/>
       <c r="AR601" s="12"/>
       <c r="AS601" s="12"/>
@@ -77977,7 +78413,7 @@
       <c r="AM602" s="12"/>
       <c r="AN602" s="12"/>
       <c r="AO602" s="39"/>
-      <c r="AP602" s="69"/>
+      <c r="AP602" s="71"/>
       <c r="AQ602" s="12"/>
       <c r="AR602" s="12"/>
       <c r="AS602" s="12"/>
@@ -78040,7 +78476,7 @@
       <c r="AM603" s="12"/>
       <c r="AN603" s="12"/>
       <c r="AO603" s="39"/>
-      <c r="AP603" s="69"/>
+      <c r="AP603" s="71"/>
       <c r="AQ603" s="12"/>
       <c r="AR603" s="12"/>
       <c r="AS603" s="12"/>
@@ -78103,7 +78539,7 @@
       <c r="AM604" s="12"/>
       <c r="AN604" s="12"/>
       <c r="AO604" s="39"/>
-      <c r="AP604" s="69"/>
+      <c r="AP604" s="71"/>
       <c r="AQ604" s="12"/>
       <c r="AR604" s="12"/>
       <c r="AS604" s="12"/>
@@ -78166,7 +78602,7 @@
       <c r="AM605" s="12"/>
       <c r="AN605" s="12"/>
       <c r="AO605" s="39"/>
-      <c r="AP605" s="69"/>
+      <c r="AP605" s="71"/>
       <c r="AQ605" s="12"/>
       <c r="AR605" s="12"/>
       <c r="AS605" s="12"/>
@@ -78229,7 +78665,7 @@
       <c r="AM606" s="12"/>
       <c r="AN606" s="12"/>
       <c r="AO606" s="39"/>
-      <c r="AP606" s="69"/>
+      <c r="AP606" s="71"/>
       <c r="AQ606" s="12"/>
       <c r="AR606" s="12"/>
       <c r="AS606" s="12"/>
@@ -78292,7 +78728,7 @@
       <c r="AM607" s="12"/>
       <c r="AN607" s="12"/>
       <c r="AO607" s="39"/>
-      <c r="AP607" s="69"/>
+      <c r="AP607" s="71"/>
       <c r="AQ607" s="12"/>
       <c r="AR607" s="12"/>
       <c r="AS607" s="12"/>
@@ -78355,7 +78791,7 @@
       <c r="AM608" s="12"/>
       <c r="AN608" s="12"/>
       <c r="AO608" s="39"/>
-      <c r="AP608" s="69"/>
+      <c r="AP608" s="71"/>
       <c r="AQ608" s="12"/>
       <c r="AR608" s="12"/>
       <c r="AS608" s="12"/>
@@ -78418,7 +78854,7 @@
       <c r="AM609" s="12"/>
       <c r="AN609" s="12"/>
       <c r="AO609" s="39"/>
-      <c r="AP609" s="69"/>
+      <c r="AP609" s="71"/>
       <c r="AQ609" s="12"/>
       <c r="AR609" s="12"/>
       <c r="AS609" s="12"/>
@@ -78481,7 +78917,7 @@
       <c r="AM610" s="12"/>
       <c r="AN610" s="12"/>
       <c r="AO610" s="39"/>
-      <c r="AP610" s="69"/>
+      <c r="AP610" s="71"/>
       <c r="AQ610" s="12"/>
       <c r="AR610" s="12"/>
       <c r="AS610" s="12"/>
@@ -78544,7 +78980,7 @@
       <c r="AM611" s="12"/>
       <c r="AN611" s="12"/>
       <c r="AO611" s="39"/>
-      <c r="AP611" s="69"/>
+      <c r="AP611" s="71"/>
       <c r="AQ611" s="12"/>
       <c r="AR611" s="12"/>
       <c r="AS611" s="12"/>
@@ -78607,7 +79043,7 @@
       <c r="AM612" s="12"/>
       <c r="AN612" s="12"/>
       <c r="AO612" s="39"/>
-      <c r="AP612" s="69"/>
+      <c r="AP612" s="71"/>
       <c r="AQ612" s="12"/>
       <c r="AR612" s="12"/>
       <c r="AS612" s="12"/>
@@ -78670,7 +79106,7 @@
       <c r="AM613" s="12"/>
       <c r="AN613" s="12"/>
       <c r="AO613" s="39"/>
-      <c r="AP613" s="69"/>
+      <c r="AP613" s="71"/>
       <c r="AQ613" s="12"/>
       <c r="AR613" s="12"/>
       <c r="AS613" s="12"/>
@@ -78733,7 +79169,7 @@
       <c r="AM614" s="12"/>
       <c r="AN614" s="12"/>
       <c r="AO614" s="39"/>
-      <c r="AP614" s="69"/>
+      <c r="AP614" s="71"/>
       <c r="AQ614" s="12"/>
       <c r="AR614" s="12"/>
       <c r="AS614" s="12"/>
@@ -78796,7 +79232,7 @@
       <c r="AM615" s="12"/>
       <c r="AN615" s="12"/>
       <c r="AO615" s="39"/>
-      <c r="AP615" s="69"/>
+      <c r="AP615" s="71"/>
       <c r="AQ615" s="12"/>
       <c r="AR615" s="12"/>
       <c r="AS615" s="12"/>
@@ -78859,7 +79295,7 @@
       <c r="AM616" s="12"/>
       <c r="AN616" s="12"/>
       <c r="AO616" s="39"/>
-      <c r="AP616" s="69"/>
+      <c r="AP616" s="71"/>
       <c r="AQ616" s="12"/>
       <c r="AR616" s="12"/>
       <c r="AS616" s="12"/>
@@ -78922,7 +79358,7 @@
       <c r="AM617" s="12"/>
       <c r="AN617" s="12"/>
       <c r="AO617" s="39"/>
-      <c r="AP617" s="69"/>
+      <c r="AP617" s="71"/>
       <c r="AQ617" s="12"/>
       <c r="AR617" s="12"/>
       <c r="AS617" s="12"/>
@@ -78985,7 +79421,7 @@
       <c r="AM618" s="12"/>
       <c r="AN618" s="12"/>
       <c r="AO618" s="39"/>
-      <c r="AP618" s="69"/>
+      <c r="AP618" s="71"/>
       <c r="AQ618" s="12"/>
       <c r="AR618" s="12"/>
       <c r="AS618" s="12"/>
@@ -79048,7 +79484,7 @@
       <c r="AM619" s="12"/>
       <c r="AN619" s="12"/>
       <c r="AO619" s="39"/>
-      <c r="AP619" s="69"/>
+      <c r="AP619" s="71"/>
       <c r="AQ619" s="12"/>
       <c r="AR619" s="12"/>
       <c r="AS619" s="12"/>
@@ -79111,7 +79547,7 @@
       <c r="AM620" s="12"/>
       <c r="AN620" s="12"/>
       <c r="AO620" s="39"/>
-      <c r="AP620" s="69"/>
+      <c r="AP620" s="71"/>
       <c r="AQ620" s="12"/>
       <c r="AR620" s="12"/>
       <c r="AS620" s="12"/>
@@ -79174,7 +79610,7 @@
       <c r="AM621" s="12"/>
       <c r="AN621" s="12"/>
       <c r="AO621" s="39"/>
-      <c r="AP621" s="69"/>
+      <c r="AP621" s="71"/>
       <c r="AQ621" s="12"/>
       <c r="AR621" s="12"/>
       <c r="AS621" s="12"/>
@@ -79237,7 +79673,7 @@
       <c r="AM622" s="12"/>
       <c r="AN622" s="12"/>
       <c r="AO622" s="39"/>
-      <c r="AP622" s="69"/>
+      <c r="AP622" s="71"/>
       <c r="AQ622" s="12"/>
       <c r="AR622" s="12"/>
       <c r="AS622" s="12"/>
@@ -79300,7 +79736,7 @@
       <c r="AM623" s="12"/>
       <c r="AN623" s="12"/>
       <c r="AO623" s="39"/>
-      <c r="AP623" s="69"/>
+      <c r="AP623" s="71"/>
       <c r="AQ623" s="12"/>
       <c r="AR623" s="12"/>
       <c r="AS623" s="12"/>
@@ -79363,7 +79799,7 @@
       <c r="AM624" s="12"/>
       <c r="AN624" s="12"/>
       <c r="AO624" s="39"/>
-      <c r="AP624" s="69"/>
+      <c r="AP624" s="71"/>
       <c r="AQ624" s="12"/>
       <c r="AR624" s="12"/>
       <c r="AS624" s="12"/>
@@ -79426,7 +79862,7 @@
       <c r="AM625" s="12"/>
       <c r="AN625" s="12"/>
       <c r="AO625" s="39"/>
-      <c r="AP625" s="69"/>
+      <c r="AP625" s="71"/>
       <c r="AQ625" s="12"/>
       <c r="AR625" s="12"/>
       <c r="AS625" s="12"/>
@@ -79489,7 +79925,7 @@
       <c r="AM626" s="12"/>
       <c r="AN626" s="12"/>
       <c r="AO626" s="39"/>
-      <c r="AP626" s="69"/>
+      <c r="AP626" s="71"/>
       <c r="AQ626" s="12"/>
       <c r="AR626" s="12"/>
       <c r="AS626" s="12"/>
@@ -79552,7 +79988,7 @@
       <c r="AM627" s="12"/>
       <c r="AN627" s="12"/>
       <c r="AO627" s="39"/>
-      <c r="AP627" s="69"/>
+      <c r="AP627" s="71"/>
       <c r="AQ627" s="12"/>
       <c r="AR627" s="12"/>
       <c r="AS627" s="12"/>
@@ -79615,7 +80051,7 @@
       <c r="AM628" s="12"/>
       <c r="AN628" s="12"/>
       <c r="AO628" s="39"/>
-      <c r="AP628" s="69"/>
+      <c r="AP628" s="71"/>
       <c r="AQ628" s="12"/>
       <c r="AR628" s="12"/>
       <c r="AS628" s="12"/>
@@ -79678,7 +80114,7 @@
       <c r="AM629" s="12"/>
       <c r="AN629" s="12"/>
       <c r="AO629" s="39"/>
-      <c r="AP629" s="69"/>
+      <c r="AP629" s="71"/>
       <c r="AQ629" s="12"/>
       <c r="AR629" s="12"/>
       <c r="AS629" s="12"/>
@@ -79741,7 +80177,7 @@
       <c r="AM630" s="12"/>
       <c r="AN630" s="12"/>
       <c r="AO630" s="39"/>
-      <c r="AP630" s="69"/>
+      <c r="AP630" s="71"/>
       <c r="AQ630" s="12"/>
       <c r="AR630" s="12"/>
       <c r="AS630" s="12"/>
@@ -79804,7 +80240,7 @@
       <c r="AM631" s="12"/>
       <c r="AN631" s="12"/>
       <c r="AO631" s="39"/>
-      <c r="AP631" s="69"/>
+      <c r="AP631" s="71"/>
       <c r="AQ631" s="12"/>
       <c r="AR631" s="12"/>
       <c r="AS631" s="12"/>
@@ -79867,7 +80303,7 @@
       <c r="AM632" s="12"/>
       <c r="AN632" s="12"/>
       <c r="AO632" s="39"/>
-      <c r="AP632" s="69"/>
+      <c r="AP632" s="71"/>
       <c r="AQ632" s="12"/>
       <c r="AR632" s="12"/>
       <c r="AS632" s="12"/>
@@ -79930,7 +80366,7 @@
       <c r="AM633" s="12"/>
       <c r="AN633" s="12"/>
       <c r="AO633" s="39"/>
-      <c r="AP633" s="69"/>
+      <c r="AP633" s="71"/>
       <c r="AQ633" s="12"/>
       <c r="AR633" s="12"/>
       <c r="AS633" s="12"/>
@@ -79993,7 +80429,7 @@
       <c r="AM634" s="12"/>
       <c r="AN634" s="12"/>
       <c r="AO634" s="39"/>
-      <c r="AP634" s="69"/>
+      <c r="AP634" s="71"/>
       <c r="AQ634" s="12"/>
       <c r="AR634" s="12"/>
       <c r="AS634" s="12"/>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -4361,22 +4361,22 @@
     <t>ds^{2} = -dt^{2} + \Phi^{2}(t)\left[2P^{-2}(\zeta,\bar{\zeta})\,d\zeta\,d\bar{\zeta} + \left\{A(r,t) + P^{-1}\left(U(r)\zeta\bar{\zeta} + V(r)\zeta + \bar{V}(r)\bar{\zeta}\right)\right\}^{2}dr^{2}\right]</t>
   </si>
   <si>
-    <t>33.44a_k1.pdf</t>
-  </si>
-  <si>
-    <t>33.44a_k1.ipynb</t>
-  </si>
-  <si>
-    <t>33.44a_k0.pdf</t>
-  </si>
-  <si>
-    <t>33.44a_k0.ipynb</t>
-  </si>
-  <si>
-    <t>33.44a_k-1.pdf</t>
-  </si>
-  <si>
-    <t>33.44a_k-1.ipynb</t>
+    <t>33.44a_1.pdf</t>
+  </si>
+  <si>
+    <t>33.44a_1.ipynb</t>
+  </si>
+  <si>
+    <t>33.44a_2.pdf</t>
+  </si>
+  <si>
+    <t>33.44a_2.ipynb</t>
+  </si>
+  <si>
+    <t>33.44a_3.pdf</t>
+  </si>
+  <si>
+    <t>33.44a_3.ipynb</t>
   </si>
   <si>
     <t>33.48</t>
@@ -64228,7 +64228,7 @@
         <v>592.0</v>
       </c>
       <c r="F412" s="14" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="G412" s="14" t="s">
         <v>283</v>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -697,7 +697,7 @@
     <t>13.3_e-1.ipynb</t>
   </si>
   <si>
-    <t>ds^{2} = -[-dt^{2}+A^{2}(t)\,dx^{2}\right]+B^{2}(t)\,e^{2x}(dy^{2}+dz^{2})</t>
+    <t>ds^{2} = -[-dt^{2}+A^{2}(t)\,dx^{2}]+B^{2}(t)\,e^{2x}(dy^{2}+dz^{2})</t>
   </si>
   <si>
     <t>13.4</t>
@@ -64087,7 +64087,7 @@
         <v>592.0</v>
       </c>
       <c r="F411" s="41" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="G411" s="14" t="s">
         <v>283</v>
@@ -64103,19 +64103,19 @@
         <v>1655</v>
       </c>
       <c r="L411" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M411" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N411" s="14" t="s">
         <v>51</v>
       </c>
       <c r="O411" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P411" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q411" s="14" t="s">
         <v>51</v>
@@ -64127,22 +64127,22 @@
         <v>51</v>
       </c>
       <c r="T411" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U411" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="V411" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="W411" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="X411" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y411" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Z411" s="14" t="s">
         <v>51</v>
@@ -64154,22 +64154,22 @@
         <v>51</v>
       </c>
       <c r="AC411" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AD411" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AE411" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AF411" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AG411" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AH411" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AI411" s="14" t="s">
         <v>51</v>
@@ -64178,13 +64178,13 @@
         <v>51</v>
       </c>
       <c r="AK411" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AL411" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AM411" s="41" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AN411" s="14" t="s">
         <v>286</v>
@@ -64295,22 +64295,22 @@
         <v>51</v>
       </c>
       <c r="AC412" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AD412" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AE412" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF412" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AG412" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AH412" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AI412" s="14" t="s">
         <v>51</v>
@@ -64319,13 +64319,13 @@
         <v>51</v>
       </c>
       <c r="AK412" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AL412" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="AM412" s="14" t="s">
-        <v>79</v>
+        <v>50</v>
+      </c>
+      <c r="AM412" s="41" t="s">
+        <v>102</v>
       </c>
       <c r="AN412" s="14" t="s">
         <v>286</v>
@@ -64387,7 +64387,7 @@
         <v>1662</v>
       </c>
       <c r="L413" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M413" s="14" t="s">
         <v>52</v>
@@ -64399,7 +64399,7 @@
         <v>52</v>
       </c>
       <c r="P413" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q413" s="14" t="s">
         <v>51</v>
@@ -64438,22 +64438,22 @@
         <v>51</v>
       </c>
       <c r="AC413" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AD413" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AE413" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF413" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AG413" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AH413" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AI413" s="14" t="s">
         <v>51</v>
@@ -64462,12 +64462,12 @@
         <v>51</v>
       </c>
       <c r="AK413" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AL413" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="AM413" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM413" s="41" t="s">
         <v>102</v>
       </c>
       <c r="AN413" s="14" t="s">

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -54345,7 +54345,7 @@
         <v>50</v>
       </c>
       <c r="R342" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S342" s="14" t="s">
         <v>50</v>
@@ -54369,7 +54369,7 @@
         <v>50</v>
       </c>
       <c r="Z342" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA342" s="14" t="s">
         <v>50</v>
@@ -54390,10 +54390,10 @@
         <v>51</v>
       </c>
       <c r="AG342" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH342" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AI342" s="14" t="s">
         <v>51</v>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -1859,10 +1859,10 @@
     <t>15.28a</t>
   </si>
   <si>
-    <t>15.28.a.pdf</t>
-  </si>
-  <si>
-    <t>15.28.a.ipynb</t>
+    <t>15.28a.pdf</t>
+  </si>
+  <si>
+    <t>15.28a.ipynb</t>
   </si>
   <si>
     <t>ds^{2} = Y^{2}(z)(dx^{2}+dy^{2})+\tfrac{1}{2}Y'(z)(dz^{2}-dt^{2})</t>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -1468,7 +1468,7 @@
     <t>14.29</t>
   </si>
   <si>
-    <t>$\text{dust for } \gamma=1$,$G^{2-\gamma} = a + 4M\tau^{2-\gamma}/(6-\gamma)$</t>
+    <t>$\text{dust for } \gamma=1 \quad G^{2-\gamma} = a + 4M\tau^{2-\gamma}/(6-\gamma)$</t>
   </si>
   <si>
     <t>14.29.pdf</t>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -2063,19 +2063,19 @@
     <t>15.85.ipynb</t>
   </si>
   <si>
+    <t>ds^{2} = \exp[b e^{-2(t-z)}]e^{2z}(a^{2}\,dz^{2} - dt^{2}) + e^{2(t+z)}(dx^{2} + dy^{2})</t>
+  </si>
+  <si>
+    <t>15.82</t>
+  </si>
+  <si>
+    <t>15.82.pdf</t>
+  </si>
+  <si>
+    <t>15.82.ipynb</t>
+  </si>
+  <si>
     <t>ds^{2} = e^{2bz} [U(dz^{2} - dt^{2}) + \sinh(2bt)(dx^{2} + dy^{2})],</t>
-  </si>
-  <si>
-    <t>15.82</t>
-  </si>
-  <si>
-    <t>15.82.pdf</t>
-  </si>
-  <si>
-    <t>15.82.ipynb</t>
-  </si>
-  <si>
-    <t>ds^{2} = \exp[b e^{-2(t-z)}]e^{2z}(a^{2}\,dz^{2} - dt^{2}) + e^{2(t+z)}(dx^{2} + dy^{2})</t>
   </si>
   <si>
     <t>15.86</t>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -2159,7 +2159,7 @@
     <t>15.90.ipynb</t>
   </si>
   <si>
-    <t>ds^{2} = tz^{m(m-1)} [dx^{2} + dy^{2}] - 2\,dz\,dt - t^{-1}(z + z^{m}t^{1/(m-1)})\,dt^{2}</t>
+    <t>ds^{2} = Y^{2}(z/t)\left[dx^{2}+dy^{2}\right]+X^{2}(z/t)\,dz^{2}-T^{2}(z/t)\,dt^{2}</t>
   </si>
   <si>
     <t>16.1</t>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -4727,16 +4727,16 @@
     <t>ds^{2} = V^{-2}(x^{\nu},x^{4})\left[\eta_{\alpha\beta}\,dx^{\alpha}\,dx^{\beta} + \varepsilon M^{2}(dx^{4})^{2}\right], \quad \eta_{\alpha\beta} = \mathrm{diag}(1,1,-\varepsilon)</t>
   </si>
   <si>
-    <t>36.16_e1.pdf</t>
-  </si>
-  <si>
-    <t>36.16_e1.ipynb</t>
-  </si>
-  <si>
-    <t>36.16_e-1.pdf</t>
-  </si>
-  <si>
-    <t>36.16_e-1.ipynb</t>
+    <t>36.16_1.pdf</t>
+  </si>
+  <si>
+    <t>36.16_1.ipynb</t>
+  </si>
+  <si>
+    <t>36.16_2.pdf</t>
+  </si>
+  <si>
+    <t>36.16_2.ipynb</t>
   </si>
   <si>
     <t>36.22</t>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15828" uniqueCount="1757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15829" uniqueCount="1757">
   <si>
     <t>Kank</t>
   </si>
@@ -32098,7 +32098,7 @@
         <v>262.0</v>
       </c>
       <c r="F185" s="16" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="G185" s="16" t="s">
         <v>283</v>
@@ -32119,8 +32119,8 @@
       <c r="M185" s="16">
         <v>0.0</v>
       </c>
-      <c r="N185" s="16">
-        <v>0.0</v>
+      <c r="N185" s="16" t="s">
+        <v>51</v>
       </c>
       <c r="O185" s="16">
         <v>0.0</v>
@@ -32195,7 +32195,7 @@
         <v>0.0</v>
       </c>
       <c r="AM185" s="16" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="AN185" s="16" t="s">
         <v>286</v>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -61178,7 +61178,7 @@
         <v>50</v>
       </c>
       <c r="Q390" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R390" s="14" t="s">
         <v>51</v>
@@ -61193,10 +61193,10 @@
         <v>52</v>
       </c>
       <c r="V390" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W390" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X390" s="14" t="s">
         <v>52</v>
@@ -61208,10 +61208,10 @@
         <v>51</v>
       </c>
       <c r="AA390" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AB390" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AC390" s="14" t="s">
         <v>50</v>
@@ -61220,22 +61220,22 @@
         <v>50</v>
       </c>
       <c r="AE390" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF390" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AG390" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AH390" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AI390" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ390" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AK390" s="14" t="s">
         <v>50</v>

--- a/metricv1.xlsx
+++ b/metricv1.xlsx
@@ -4637,7 +4637,7 @@
     <t>$b=\frac{a-1}{2a-1}, \; c=4a$</t>
   </si>
   <si>
-    <t>35_76_2.pdf</t>
+    <t>35.76_2.pdf</t>
   </si>
   <si>
     <t>35.76_2.ipynb</t>
